--- a/saida/F0009_000/Comparativo Cronograma 08-07-2026.xlsx
+++ b/saida/F0009_000/Comparativo Cronograma 08-07-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bureauveritas.sharepoint.com/teams/POP-Planejamento/Shared Documents/Automacoes/Comparativo_Cronograma/saida/F0009_000/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="11_EED48E6AFF43D7375227193631D5E912D2F457D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73168A04-F02A-48BD-B07A-B1C979B207A6}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="11_EED48E6AFF43D7375227193631D5E912D2F457D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D00DF041-AAAB-4975-80BE-9CDDA76FD9AC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
@@ -21,9 +21,6 @@
     <sheet name="Sprint Atual" sheetId="6" r:id="rId6"/>
     <sheet name="Próximo Sprint" sheetId="7" r:id="rId7"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId8"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -42,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3619" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3606" uniqueCount="475">
   <si>
     <t>Id</t>
   </si>
@@ -1451,22 +1448,22 @@
     <t>COMP_AP</t>
   </si>
   <si>
-    <t>Soma</t>
-  </si>
-  <si>
-    <t>Média</t>
-  </si>
-  <si>
-    <t>Soma Acumulada</t>
-  </si>
-  <si>
-    <t>Contagem</t>
-  </si>
-  <si>
     <t>Coluna1</t>
   </si>
   <si>
     <t>TOTAL</t>
+  </si>
+  <si>
+    <t>FIM DE PROJETO</t>
+  </si>
+  <si>
+    <t>CONFIRMAR</t>
+  </si>
+  <si>
+    <t>CONFIRMAR 02/07</t>
+  </si>
+  <si>
+    <t>REPROGRAMAR</t>
   </si>
 </sst>
 </file>
@@ -1475,7 +1472,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -1520,7 +1517,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1531,7 +1528,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1555,12 +1552,15 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="161">
+  <dxfs count="162">
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1589,23 +1589,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1691,15 +1674,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1713,14 +1688,158 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1797,164 +1916,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.0%"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.0%"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.0%"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.0%"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1966,9 +1927,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2033,7 +1991,52 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -19057,4105 +19060,104 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Base"/>
-      <sheetName val="Resumo"/>
-      <sheetName val="Curva S"/>
-      <sheetName val="Concluídas"/>
-      <sheetName val="Atrasadas"/>
-      <sheetName val="Sprint Atual"/>
-      <sheetName val="Próximo Sprint"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>Emissão inicial total</v>
-          </cell>
-          <cell r="C3" t="str">
-            <v>Emissão inicial concluída</v>
-          </cell>
-          <cell r="D3" t="str">
-            <v>%EI</v>
-          </cell>
-          <cell r="E3" t="str">
-            <v>Avaliação do cliente concluída</v>
-          </cell>
-          <cell r="F3" t="str">
-            <v>Atendimento de comentário concluído</v>
-          </cell>
-          <cell r="G3" t="str">
-            <v>Aprovação concluída</v>
-          </cell>
-          <cell r="H3" t="str">
-            <v>%AP</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>AUTOMAÇÃO E INSTRUMENTAÇÃO</v>
-          </cell>
-          <cell r="B4">
-            <v>42</v>
-          </cell>
-          <cell r="C4">
-            <v>37</v>
-          </cell>
-          <cell r="D4">
-            <v>0.88095238095238093</v>
-          </cell>
-          <cell r="E4">
-            <v>3</v>
-          </cell>
-          <cell r="F4">
-            <v>0</v>
-          </cell>
-          <cell r="G4">
-            <v>0</v>
-          </cell>
-          <cell r="H4">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>CIVIL</v>
-          </cell>
-          <cell r="B5">
-            <v>2</v>
-          </cell>
-          <cell r="C5">
-            <v>0</v>
-          </cell>
-          <cell r="D5">
-            <v>0</v>
-          </cell>
-          <cell r="E5">
-            <v>0</v>
-          </cell>
-          <cell r="F5">
-            <v>0</v>
-          </cell>
-          <cell r="G5">
-            <v>0</v>
-          </cell>
-          <cell r="H5">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>COORDENAÇÃO</v>
-          </cell>
-          <cell r="B6">
-            <v>3</v>
-          </cell>
-          <cell r="C6">
-            <v>1</v>
-          </cell>
-          <cell r="D6">
-            <v>0.33333333333333331</v>
-          </cell>
-          <cell r="E6">
-            <v>1</v>
-          </cell>
-          <cell r="F6">
-            <v>0</v>
-          </cell>
-          <cell r="G6">
-            <v>0</v>
-          </cell>
-          <cell r="H6">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>ELÉTRICA</v>
-          </cell>
-          <cell r="B7">
-            <v>3</v>
-          </cell>
-          <cell r="C7">
-            <v>3</v>
-          </cell>
-          <cell r="D7">
-            <v>1</v>
-          </cell>
-          <cell r="E7">
-            <v>2</v>
-          </cell>
-          <cell r="F7">
-            <v>0</v>
-          </cell>
-          <cell r="G7">
-            <v>0</v>
-          </cell>
-          <cell r="H7">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>ESTRUTURA METÁLICA</v>
-          </cell>
-          <cell r="B8">
-            <v>14</v>
-          </cell>
-          <cell r="C8">
-            <v>0</v>
-          </cell>
-          <cell r="D8">
-            <v>0</v>
-          </cell>
-          <cell r="E8">
-            <v>0</v>
-          </cell>
-          <cell r="F8">
-            <v>0</v>
-          </cell>
-          <cell r="G8">
-            <v>0</v>
-          </cell>
-          <cell r="H8">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>GERAL</v>
-          </cell>
-          <cell r="B9">
-            <v>0</v>
-          </cell>
-          <cell r="C9">
-            <v>0</v>
-          </cell>
-          <cell r="D9">
-            <v>0</v>
-          </cell>
-          <cell r="E9">
-            <v>0</v>
-          </cell>
-          <cell r="F9">
-            <v>0</v>
-          </cell>
-          <cell r="G9">
-            <v>0</v>
-          </cell>
-          <cell r="H9">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>MARCOS</v>
-          </cell>
-          <cell r="B10">
-            <v>0</v>
-          </cell>
-          <cell r="C10">
-            <v>0</v>
-          </cell>
-          <cell r="D10">
-            <v>0</v>
-          </cell>
-          <cell r="E10">
-            <v>0</v>
-          </cell>
-          <cell r="F10">
-            <v>0</v>
-          </cell>
-          <cell r="G10">
-            <v>0</v>
-          </cell>
-          <cell r="H10">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>MECÂNICA</v>
-          </cell>
-          <cell r="B11">
-            <v>25</v>
-          </cell>
-          <cell r="C11">
-            <v>16</v>
-          </cell>
-          <cell r="D11">
-            <v>0.64</v>
-          </cell>
-          <cell r="E11">
-            <v>4</v>
-          </cell>
-          <cell r="F11">
-            <v>1</v>
-          </cell>
-          <cell r="G11">
-            <v>1</v>
-          </cell>
-          <cell r="H11">
-            <v>0.04</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12" t="str">
-            <v>PENDÊNCIAS</v>
-          </cell>
-          <cell r="B12">
-            <v>0</v>
-          </cell>
-          <cell r="C12">
-            <v>0</v>
-          </cell>
-          <cell r="D12">
-            <v>0</v>
-          </cell>
-          <cell r="E12">
-            <v>0</v>
-          </cell>
-          <cell r="F12">
-            <v>0</v>
-          </cell>
-          <cell r="G12">
-            <v>0</v>
-          </cell>
-          <cell r="H12">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13" t="str">
-            <v>PLANEJAMENTO</v>
-          </cell>
-          <cell r="B13">
-            <v>2</v>
-          </cell>
-          <cell r="C13">
-            <v>2</v>
-          </cell>
-          <cell r="D13">
-            <v>1</v>
-          </cell>
-          <cell r="E13">
-            <v>2</v>
-          </cell>
-          <cell r="F13">
-            <v>2</v>
-          </cell>
-          <cell r="G13">
-            <v>2</v>
-          </cell>
-          <cell r="H13">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14" t="str">
-            <v>PROCESSOS</v>
-          </cell>
-          <cell r="B14">
-            <v>1</v>
-          </cell>
-          <cell r="C14">
-            <v>1</v>
-          </cell>
-          <cell r="D14">
-            <v>1</v>
-          </cell>
-          <cell r="E14">
-            <v>1</v>
-          </cell>
-          <cell r="F14">
-            <v>0</v>
-          </cell>
-          <cell r="G14">
-            <v>0</v>
-          </cell>
-          <cell r="H14">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15" t="str">
-            <v>TUBULAÇÃO / UTILIDADES</v>
-          </cell>
-          <cell r="B15">
-            <v>13</v>
-          </cell>
-          <cell r="C15">
-            <v>1</v>
-          </cell>
-          <cell r="D15">
-            <v>7.6923076923076927E-2</v>
-          </cell>
-          <cell r="E15">
-            <v>1</v>
-          </cell>
-          <cell r="F15">
-            <v>0</v>
-          </cell>
-          <cell r="G15">
-            <v>0</v>
-          </cell>
-          <cell r="H15">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="B21" t="str">
-            <v>Emissão Inicial Atrasada</v>
-          </cell>
-          <cell r="C21" t="str">
-            <v>Avaliação Cliente Atrasada</v>
-          </cell>
-          <cell r="D21" t="str">
-            <v>Atendimento Atrasado</v>
-          </cell>
-          <cell r="E21" t="str">
-            <v>Aprovação Atrasada</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22" t="str">
-            <v>AUTOMAÇÃO E INSTRUMENTAÇÃO</v>
-          </cell>
-          <cell r="B22">
-            <v>3</v>
-          </cell>
-          <cell r="C22">
-            <v>30</v>
-          </cell>
-          <cell r="D22">
-            <v>32</v>
-          </cell>
-          <cell r="E22">
-            <v>32</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23" t="str">
-            <v>CIVIL</v>
-          </cell>
-          <cell r="B23">
-            <v>0</v>
-          </cell>
-          <cell r="C23">
-            <v>0</v>
-          </cell>
-          <cell r="D23">
-            <v>0</v>
-          </cell>
-          <cell r="E23">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24" t="str">
-            <v>COORDENAÇÃO</v>
-          </cell>
-          <cell r="B24">
-            <v>1</v>
-          </cell>
-          <cell r="C24">
-            <v>0</v>
-          </cell>
-          <cell r="D24">
-            <v>0</v>
-          </cell>
-          <cell r="E24">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25" t="str">
-            <v>ELÉTRICA</v>
-          </cell>
-          <cell r="B25">
-            <v>0</v>
-          </cell>
-          <cell r="C25">
-            <v>0</v>
-          </cell>
-          <cell r="D25">
-            <v>2</v>
-          </cell>
-          <cell r="E25">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26" t="str">
-            <v>ESTRUTURA METÁLICA</v>
-          </cell>
-          <cell r="B26">
-            <v>0</v>
-          </cell>
-          <cell r="C26">
-            <v>0</v>
-          </cell>
-          <cell r="D26">
-            <v>0</v>
-          </cell>
-          <cell r="E26">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27" t="str">
-            <v>GERAL</v>
-          </cell>
-          <cell r="B27">
-            <v>0</v>
-          </cell>
-          <cell r="C27">
-            <v>0</v>
-          </cell>
-          <cell r="D27">
-            <v>0</v>
-          </cell>
-          <cell r="E27">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28" t="str">
-            <v>MARCOS</v>
-          </cell>
-          <cell r="B28">
-            <v>0</v>
-          </cell>
-          <cell r="C28">
-            <v>0</v>
-          </cell>
-          <cell r="D28">
-            <v>0</v>
-          </cell>
-          <cell r="E28">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29" t="str">
-            <v>MECÂNICA</v>
-          </cell>
-          <cell r="B29">
-            <v>1</v>
-          </cell>
-          <cell r="C29">
-            <v>11</v>
-          </cell>
-          <cell r="D29">
-            <v>14</v>
-          </cell>
-          <cell r="E29">
-            <v>8</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30" t="str">
-            <v>PENDÊNCIAS</v>
-          </cell>
-          <cell r="B30">
-            <v>0</v>
-          </cell>
-          <cell r="C30">
-            <v>0</v>
-          </cell>
-          <cell r="D30">
-            <v>0</v>
-          </cell>
-          <cell r="E30">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31" t="str">
-            <v>PLANEJAMENTO</v>
-          </cell>
-          <cell r="B31">
-            <v>0</v>
-          </cell>
-          <cell r="C31">
-            <v>0</v>
-          </cell>
-          <cell r="D31">
-            <v>0</v>
-          </cell>
-          <cell r="E31">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32" t="str">
-            <v>PROCESSOS</v>
-          </cell>
-          <cell r="B32">
-            <v>0</v>
-          </cell>
-          <cell r="C32">
-            <v>0</v>
-          </cell>
-          <cell r="D32">
-            <v>1</v>
-          </cell>
-          <cell r="E32">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33" t="str">
-            <v>TUBULAÇÃO / UTILIDADES</v>
-          </cell>
-          <cell r="B33">
-            <v>1</v>
-          </cell>
-          <cell r="C33">
-            <v>0</v>
-          </cell>
-          <cell r="D33">
-            <v>1</v>
-          </cell>
-          <cell r="E33">
-            <v>1</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2">
-        <row r="1">
-          <cell r="B1" t="str">
-            <v>Emissão prevista na LB</v>
-          </cell>
-          <cell r="C1" t="str">
-            <v>Emissão prevista na LB acumulada</v>
-          </cell>
-          <cell r="D1" t="str">
-            <v>Emissão realizada por dia</v>
-          </cell>
-          <cell r="E1" t="str">
-            <v>Emissão realizada acumulada</v>
-          </cell>
-          <cell r="F1" t="str">
-            <v>Aprovação prevista na LB</v>
-          </cell>
-          <cell r="G1" t="str">
-            <v>Aprovação realizada por dia</v>
-          </cell>
-          <cell r="H1" t="str">
-            <v>Aprovação prevista na LB acumulada</v>
-          </cell>
-          <cell r="I1" t="str">
-            <v>Aprovação realizada acumulada</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="A2">
-            <v>46101</v>
-          </cell>
-          <cell r="B2">
-            <v>0</v>
-          </cell>
-          <cell r="C2">
-            <v>0</v>
-          </cell>
-          <cell r="D2">
-            <v>0</v>
-          </cell>
-          <cell r="E2">
-            <v>0</v>
-          </cell>
-          <cell r="F2">
-            <v>0</v>
-          </cell>
-          <cell r="G2">
-            <v>0</v>
-          </cell>
-          <cell r="H2">
-            <v>0</v>
-          </cell>
-          <cell r="I2">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3">
-            <v>46102</v>
-          </cell>
-          <cell r="B3">
-            <v>0</v>
-          </cell>
-          <cell r="C3">
-            <v>0</v>
-          </cell>
-          <cell r="D3">
-            <v>0</v>
-          </cell>
-          <cell r="E3">
-            <v>0</v>
-          </cell>
-          <cell r="F3">
-            <v>0</v>
-          </cell>
-          <cell r="G3">
-            <v>0</v>
-          </cell>
-          <cell r="H3">
-            <v>0</v>
-          </cell>
-          <cell r="I3">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4">
-            <v>46103</v>
-          </cell>
-          <cell r="B4">
-            <v>0</v>
-          </cell>
-          <cell r="C4">
-            <v>0</v>
-          </cell>
-          <cell r="D4">
-            <v>0</v>
-          </cell>
-          <cell r="E4">
-            <v>0</v>
-          </cell>
-          <cell r="F4">
-            <v>0</v>
-          </cell>
-          <cell r="G4">
-            <v>0</v>
-          </cell>
-          <cell r="H4">
-            <v>0</v>
-          </cell>
-          <cell r="I4">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5">
-            <v>46104</v>
-          </cell>
-          <cell r="B5">
-            <v>0</v>
-          </cell>
-          <cell r="C5">
-            <v>0</v>
-          </cell>
-          <cell r="D5">
-            <v>0</v>
-          </cell>
-          <cell r="E5">
-            <v>0</v>
-          </cell>
-          <cell r="F5">
-            <v>0</v>
-          </cell>
-          <cell r="G5">
-            <v>0</v>
-          </cell>
-          <cell r="H5">
-            <v>0</v>
-          </cell>
-          <cell r="I5">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6">
-            <v>46105</v>
-          </cell>
-          <cell r="B6">
-            <v>0</v>
-          </cell>
-          <cell r="C6">
-            <v>0</v>
-          </cell>
-          <cell r="D6">
-            <v>0</v>
-          </cell>
-          <cell r="E6">
-            <v>0</v>
-          </cell>
-          <cell r="F6">
-            <v>0</v>
-          </cell>
-          <cell r="G6">
-            <v>0</v>
-          </cell>
-          <cell r="H6">
-            <v>0</v>
-          </cell>
-          <cell r="I6">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7">
-            <v>46106</v>
-          </cell>
-          <cell r="B7">
-            <v>0</v>
-          </cell>
-          <cell r="C7">
-            <v>0</v>
-          </cell>
-          <cell r="D7">
-            <v>0</v>
-          </cell>
-          <cell r="E7">
-            <v>0</v>
-          </cell>
-          <cell r="F7">
-            <v>0</v>
-          </cell>
-          <cell r="G7">
-            <v>0</v>
-          </cell>
-          <cell r="H7">
-            <v>0</v>
-          </cell>
-          <cell r="I7">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8">
-            <v>46107</v>
-          </cell>
-          <cell r="B8">
-            <v>0</v>
-          </cell>
-          <cell r="C8">
-            <v>0</v>
-          </cell>
-          <cell r="D8">
-            <v>0</v>
-          </cell>
-          <cell r="E8">
-            <v>0</v>
-          </cell>
-          <cell r="F8">
-            <v>0</v>
-          </cell>
-          <cell r="G8">
-            <v>0</v>
-          </cell>
-          <cell r="H8">
-            <v>0</v>
-          </cell>
-          <cell r="I8">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9">
-            <v>46108</v>
-          </cell>
-          <cell r="B9">
-            <v>0</v>
-          </cell>
-          <cell r="C9">
-            <v>0</v>
-          </cell>
-          <cell r="D9">
-            <v>0</v>
-          </cell>
-          <cell r="E9">
-            <v>0</v>
-          </cell>
-          <cell r="F9">
-            <v>0</v>
-          </cell>
-          <cell r="G9">
-            <v>0</v>
-          </cell>
-          <cell r="H9">
-            <v>0</v>
-          </cell>
-          <cell r="I9">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10">
-            <v>46109</v>
-          </cell>
-          <cell r="B10">
-            <v>0</v>
-          </cell>
-          <cell r="C10">
-            <v>0</v>
-          </cell>
-          <cell r="D10">
-            <v>0</v>
-          </cell>
-          <cell r="E10">
-            <v>0</v>
-          </cell>
-          <cell r="F10">
-            <v>0</v>
-          </cell>
-          <cell r="G10">
-            <v>0</v>
-          </cell>
-          <cell r="H10">
-            <v>0</v>
-          </cell>
-          <cell r="I10">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11">
-            <v>46110</v>
-          </cell>
-          <cell r="B11">
-            <v>0</v>
-          </cell>
-          <cell r="C11">
-            <v>0</v>
-          </cell>
-          <cell r="D11">
-            <v>0</v>
-          </cell>
-          <cell r="E11">
-            <v>0</v>
-          </cell>
-          <cell r="F11">
-            <v>0</v>
-          </cell>
-          <cell r="G11">
-            <v>0</v>
-          </cell>
-          <cell r="H11">
-            <v>0</v>
-          </cell>
-          <cell r="I11">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12">
-            <v>46111</v>
-          </cell>
-          <cell r="B12">
-            <v>0</v>
-          </cell>
-          <cell r="C12">
-            <v>0</v>
-          </cell>
-          <cell r="D12">
-            <v>0</v>
-          </cell>
-          <cell r="E12">
-            <v>0</v>
-          </cell>
-          <cell r="F12">
-            <v>0</v>
-          </cell>
-          <cell r="G12">
-            <v>0</v>
-          </cell>
-          <cell r="H12">
-            <v>0</v>
-          </cell>
-          <cell r="I12">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13">
-            <v>46112</v>
-          </cell>
-          <cell r="B13">
-            <v>0</v>
-          </cell>
-          <cell r="C13">
-            <v>0</v>
-          </cell>
-          <cell r="D13">
-            <v>0</v>
-          </cell>
-          <cell r="E13">
-            <v>0</v>
-          </cell>
-          <cell r="F13">
-            <v>0</v>
-          </cell>
-          <cell r="G13">
-            <v>0</v>
-          </cell>
-          <cell r="H13">
-            <v>0</v>
-          </cell>
-          <cell r="I13">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14">
-            <v>46113</v>
-          </cell>
-          <cell r="B14">
-            <v>0</v>
-          </cell>
-          <cell r="C14">
-            <v>0</v>
-          </cell>
-          <cell r="D14">
-            <v>0</v>
-          </cell>
-          <cell r="E14">
-            <v>0</v>
-          </cell>
-          <cell r="F14">
-            <v>0</v>
-          </cell>
-          <cell r="G14">
-            <v>0</v>
-          </cell>
-          <cell r="H14">
-            <v>0</v>
-          </cell>
-          <cell r="I14">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15">
-            <v>46114</v>
-          </cell>
-          <cell r="B15">
-            <v>0</v>
-          </cell>
-          <cell r="C15">
-            <v>0</v>
-          </cell>
-          <cell r="D15">
-            <v>0</v>
-          </cell>
-          <cell r="E15">
-            <v>0</v>
-          </cell>
-          <cell r="F15">
-            <v>0</v>
-          </cell>
-          <cell r="G15">
-            <v>0</v>
-          </cell>
-          <cell r="H15">
-            <v>0</v>
-          </cell>
-          <cell r="I15">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16">
-            <v>46115</v>
-          </cell>
-          <cell r="B16">
-            <v>0</v>
-          </cell>
-          <cell r="C16">
-            <v>0</v>
-          </cell>
-          <cell r="D16">
-            <v>0</v>
-          </cell>
-          <cell r="E16">
-            <v>0</v>
-          </cell>
-          <cell r="F16">
-            <v>0</v>
-          </cell>
-          <cell r="G16">
-            <v>0</v>
-          </cell>
-          <cell r="H16">
-            <v>0</v>
-          </cell>
-          <cell r="I16">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17">
-            <v>46116</v>
-          </cell>
-          <cell r="B17">
-            <v>0</v>
-          </cell>
-          <cell r="C17">
-            <v>0</v>
-          </cell>
-          <cell r="D17">
-            <v>0</v>
-          </cell>
-          <cell r="E17">
-            <v>0</v>
-          </cell>
-          <cell r="F17">
-            <v>0</v>
-          </cell>
-          <cell r="G17">
-            <v>0</v>
-          </cell>
-          <cell r="H17">
-            <v>0</v>
-          </cell>
-          <cell r="I17">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18">
-            <v>46117</v>
-          </cell>
-          <cell r="B18">
-            <v>0</v>
-          </cell>
-          <cell r="C18">
-            <v>0</v>
-          </cell>
-          <cell r="D18">
-            <v>0</v>
-          </cell>
-          <cell r="E18">
-            <v>0</v>
-          </cell>
-          <cell r="F18">
-            <v>0</v>
-          </cell>
-          <cell r="G18">
-            <v>0</v>
-          </cell>
-          <cell r="H18">
-            <v>0</v>
-          </cell>
-          <cell r="I18">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19">
-            <v>46118</v>
-          </cell>
-          <cell r="B19">
-            <v>0</v>
-          </cell>
-          <cell r="C19">
-            <v>0</v>
-          </cell>
-          <cell r="D19">
-            <v>0</v>
-          </cell>
-          <cell r="E19">
-            <v>0</v>
-          </cell>
-          <cell r="F19">
-            <v>0</v>
-          </cell>
-          <cell r="G19">
-            <v>0</v>
-          </cell>
-          <cell r="H19">
-            <v>0</v>
-          </cell>
-          <cell r="I19">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20">
-            <v>46119</v>
-          </cell>
-          <cell r="B20">
-            <v>0</v>
-          </cell>
-          <cell r="C20">
-            <v>0</v>
-          </cell>
-          <cell r="D20">
-            <v>0</v>
-          </cell>
-          <cell r="E20">
-            <v>0</v>
-          </cell>
-          <cell r="F20">
-            <v>0</v>
-          </cell>
-          <cell r="G20">
-            <v>0</v>
-          </cell>
-          <cell r="H20">
-            <v>0</v>
-          </cell>
-          <cell r="I20">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21">
-            <v>46120</v>
-          </cell>
-          <cell r="B21">
-            <v>0</v>
-          </cell>
-          <cell r="C21">
-            <v>0</v>
-          </cell>
-          <cell r="D21">
-            <v>0</v>
-          </cell>
-          <cell r="E21">
-            <v>0</v>
-          </cell>
-          <cell r="F21">
-            <v>0</v>
-          </cell>
-          <cell r="G21">
-            <v>0</v>
-          </cell>
-          <cell r="H21">
-            <v>0</v>
-          </cell>
-          <cell r="I21">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22">
-            <v>46121</v>
-          </cell>
-          <cell r="B22">
-            <v>0</v>
-          </cell>
-          <cell r="C22">
-            <v>0</v>
-          </cell>
-          <cell r="D22">
-            <v>0</v>
-          </cell>
-          <cell r="E22">
-            <v>0</v>
-          </cell>
-          <cell r="F22">
-            <v>0</v>
-          </cell>
-          <cell r="G22">
-            <v>0</v>
-          </cell>
-          <cell r="H22">
-            <v>0</v>
-          </cell>
-          <cell r="I22">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23">
-            <v>46122</v>
-          </cell>
-          <cell r="B23">
-            <v>0</v>
-          </cell>
-          <cell r="C23">
-            <v>0</v>
-          </cell>
-          <cell r="D23">
-            <v>0</v>
-          </cell>
-          <cell r="E23">
-            <v>0</v>
-          </cell>
-          <cell r="F23">
-            <v>0</v>
-          </cell>
-          <cell r="G23">
-            <v>0</v>
-          </cell>
-          <cell r="H23">
-            <v>0</v>
-          </cell>
-          <cell r="I23">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24">
-            <v>46123</v>
-          </cell>
-          <cell r="B24">
-            <v>0</v>
-          </cell>
-          <cell r="C24">
-            <v>0</v>
-          </cell>
-          <cell r="D24">
-            <v>0</v>
-          </cell>
-          <cell r="E24">
-            <v>0</v>
-          </cell>
-          <cell r="F24">
-            <v>0</v>
-          </cell>
-          <cell r="G24">
-            <v>0</v>
-          </cell>
-          <cell r="H24">
-            <v>0</v>
-          </cell>
-          <cell r="I24">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25">
-            <v>46124</v>
-          </cell>
-          <cell r="B25">
-            <v>0</v>
-          </cell>
-          <cell r="C25">
-            <v>0</v>
-          </cell>
-          <cell r="D25">
-            <v>0</v>
-          </cell>
-          <cell r="E25">
-            <v>0</v>
-          </cell>
-          <cell r="F25">
-            <v>0</v>
-          </cell>
-          <cell r="G25">
-            <v>0</v>
-          </cell>
-          <cell r="H25">
-            <v>0</v>
-          </cell>
-          <cell r="I25">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26">
-            <v>46125</v>
-          </cell>
-          <cell r="B26">
-            <v>0</v>
-          </cell>
-          <cell r="C26">
-            <v>0</v>
-          </cell>
-          <cell r="D26">
-            <v>0</v>
-          </cell>
-          <cell r="E26">
-            <v>0</v>
-          </cell>
-          <cell r="F26">
-            <v>0</v>
-          </cell>
-          <cell r="G26">
-            <v>0</v>
-          </cell>
-          <cell r="H26">
-            <v>0</v>
-          </cell>
-          <cell r="I26">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27">
-            <v>46126</v>
-          </cell>
-          <cell r="B27">
-            <v>0</v>
-          </cell>
-          <cell r="C27">
-            <v>0</v>
-          </cell>
-          <cell r="D27">
-            <v>0</v>
-          </cell>
-          <cell r="E27">
-            <v>0</v>
-          </cell>
-          <cell r="F27">
-            <v>0</v>
-          </cell>
-          <cell r="G27">
-            <v>0</v>
-          </cell>
-          <cell r="H27">
-            <v>0</v>
-          </cell>
-          <cell r="I27">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28">
-            <v>46127</v>
-          </cell>
-          <cell r="B28">
-            <v>0</v>
-          </cell>
-          <cell r="C28">
-            <v>0</v>
-          </cell>
-          <cell r="D28">
-            <v>0</v>
-          </cell>
-          <cell r="E28">
-            <v>0</v>
-          </cell>
-          <cell r="F28">
-            <v>0</v>
-          </cell>
-          <cell r="G28">
-            <v>0</v>
-          </cell>
-          <cell r="H28">
-            <v>0</v>
-          </cell>
-          <cell r="I28">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29">
-            <v>46128</v>
-          </cell>
-          <cell r="B29">
-            <v>0</v>
-          </cell>
-          <cell r="C29">
-            <v>0</v>
-          </cell>
-          <cell r="D29">
-            <v>0</v>
-          </cell>
-          <cell r="E29">
-            <v>0</v>
-          </cell>
-          <cell r="F29">
-            <v>0</v>
-          </cell>
-          <cell r="G29">
-            <v>0</v>
-          </cell>
-          <cell r="H29">
-            <v>0</v>
-          </cell>
-          <cell r="I29">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30">
-            <v>46129</v>
-          </cell>
-          <cell r="B30">
-            <v>0</v>
-          </cell>
-          <cell r="C30">
-            <v>0</v>
-          </cell>
-          <cell r="D30">
-            <v>0</v>
-          </cell>
-          <cell r="E30">
-            <v>0</v>
-          </cell>
-          <cell r="F30">
-            <v>0</v>
-          </cell>
-          <cell r="G30">
-            <v>0</v>
-          </cell>
-          <cell r="H30">
-            <v>0</v>
-          </cell>
-          <cell r="I30">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31">
-            <v>46130</v>
-          </cell>
-          <cell r="B31">
-            <v>0</v>
-          </cell>
-          <cell r="C31">
-            <v>0</v>
-          </cell>
-          <cell r="D31">
-            <v>0</v>
-          </cell>
-          <cell r="E31">
-            <v>0</v>
-          </cell>
-          <cell r="F31">
-            <v>0</v>
-          </cell>
-          <cell r="G31">
-            <v>0</v>
-          </cell>
-          <cell r="H31">
-            <v>0</v>
-          </cell>
-          <cell r="I31">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32">
-            <v>46131</v>
-          </cell>
-          <cell r="B32">
-            <v>0</v>
-          </cell>
-          <cell r="C32">
-            <v>0</v>
-          </cell>
-          <cell r="D32">
-            <v>0</v>
-          </cell>
-          <cell r="E32">
-            <v>0</v>
-          </cell>
-          <cell r="F32">
-            <v>0</v>
-          </cell>
-          <cell r="G32">
-            <v>0</v>
-          </cell>
-          <cell r="H32">
-            <v>0</v>
-          </cell>
-          <cell r="I32">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33">
-            <v>46132</v>
-          </cell>
-          <cell r="B33">
-            <v>0</v>
-          </cell>
-          <cell r="C33">
-            <v>0</v>
-          </cell>
-          <cell r="D33">
-            <v>0</v>
-          </cell>
-          <cell r="E33">
-            <v>0</v>
-          </cell>
-          <cell r="F33">
-            <v>0</v>
-          </cell>
-          <cell r="G33">
-            <v>0</v>
-          </cell>
-          <cell r="H33">
-            <v>0</v>
-          </cell>
-          <cell r="I33">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="A34">
-            <v>46133</v>
-          </cell>
-          <cell r="B34">
-            <v>0</v>
-          </cell>
-          <cell r="C34">
-            <v>0</v>
-          </cell>
-          <cell r="D34">
-            <v>0</v>
-          </cell>
-          <cell r="E34">
-            <v>0</v>
-          </cell>
-          <cell r="F34">
-            <v>0</v>
-          </cell>
-          <cell r="G34">
-            <v>0</v>
-          </cell>
-          <cell r="H34">
-            <v>0</v>
-          </cell>
-          <cell r="I34">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="A35">
-            <v>46134</v>
-          </cell>
-          <cell r="B35">
-            <v>0</v>
-          </cell>
-          <cell r="C35">
-            <v>0</v>
-          </cell>
-          <cell r="D35">
-            <v>0</v>
-          </cell>
-          <cell r="E35">
-            <v>0</v>
-          </cell>
-          <cell r="F35">
-            <v>0</v>
-          </cell>
-          <cell r="G35">
-            <v>0</v>
-          </cell>
-          <cell r="H35">
-            <v>0</v>
-          </cell>
-          <cell r="I35">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36">
-            <v>46135</v>
-          </cell>
-          <cell r="B36">
-            <v>0</v>
-          </cell>
-          <cell r="C36">
-            <v>0</v>
-          </cell>
-          <cell r="D36">
-            <v>0</v>
-          </cell>
-          <cell r="E36">
-            <v>0</v>
-          </cell>
-          <cell r="F36">
-            <v>0</v>
-          </cell>
-          <cell r="G36">
-            <v>0</v>
-          </cell>
-          <cell r="H36">
-            <v>0</v>
-          </cell>
-          <cell r="I36">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37">
-            <v>46136</v>
-          </cell>
-          <cell r="B37">
-            <v>0</v>
-          </cell>
-          <cell r="C37">
-            <v>0</v>
-          </cell>
-          <cell r="D37">
-            <v>0</v>
-          </cell>
-          <cell r="E37">
-            <v>0</v>
-          </cell>
-          <cell r="F37">
-            <v>0</v>
-          </cell>
-          <cell r="G37">
-            <v>0</v>
-          </cell>
-          <cell r="H37">
-            <v>0</v>
-          </cell>
-          <cell r="I37">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38">
-            <v>46137</v>
-          </cell>
-          <cell r="B38">
-            <v>0</v>
-          </cell>
-          <cell r="C38">
-            <v>0</v>
-          </cell>
-          <cell r="D38">
-            <v>0</v>
-          </cell>
-          <cell r="E38">
-            <v>0</v>
-          </cell>
-          <cell r="F38">
-            <v>0</v>
-          </cell>
-          <cell r="G38">
-            <v>0</v>
-          </cell>
-          <cell r="H38">
-            <v>0</v>
-          </cell>
-          <cell r="I38">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="A39">
-            <v>46138</v>
-          </cell>
-          <cell r="B39">
-            <v>0</v>
-          </cell>
-          <cell r="C39">
-            <v>0</v>
-          </cell>
-          <cell r="D39">
-            <v>0</v>
-          </cell>
-          <cell r="E39">
-            <v>0</v>
-          </cell>
-          <cell r="F39">
-            <v>0</v>
-          </cell>
-          <cell r="G39">
-            <v>0</v>
-          </cell>
-          <cell r="H39">
-            <v>0</v>
-          </cell>
-          <cell r="I39">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="A40">
-            <v>46139</v>
-          </cell>
-          <cell r="B40">
-            <v>0</v>
-          </cell>
-          <cell r="C40">
-            <v>0</v>
-          </cell>
-          <cell r="D40">
-            <v>0</v>
-          </cell>
-          <cell r="E40">
-            <v>0</v>
-          </cell>
-          <cell r="F40">
-            <v>0</v>
-          </cell>
-          <cell r="G40">
-            <v>0</v>
-          </cell>
-          <cell r="H40">
-            <v>0</v>
-          </cell>
-          <cell r="I40">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="A41">
-            <v>46140</v>
-          </cell>
-          <cell r="B41">
-            <v>0</v>
-          </cell>
-          <cell r="C41">
-            <v>0</v>
-          </cell>
-          <cell r="D41">
-            <v>0</v>
-          </cell>
-          <cell r="E41">
-            <v>0</v>
-          </cell>
-          <cell r="F41">
-            <v>0</v>
-          </cell>
-          <cell r="G41">
-            <v>0</v>
-          </cell>
-          <cell r="H41">
-            <v>0</v>
-          </cell>
-          <cell r="I41">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="A42">
-            <v>46141</v>
-          </cell>
-          <cell r="B42">
-            <v>2</v>
-          </cell>
-          <cell r="C42">
-            <v>2</v>
-          </cell>
-          <cell r="D42">
-            <v>2</v>
-          </cell>
-          <cell r="E42">
-            <v>2</v>
-          </cell>
-          <cell r="F42">
-            <v>0</v>
-          </cell>
-          <cell r="G42">
-            <v>0</v>
-          </cell>
-          <cell r="H42">
-            <v>0</v>
-          </cell>
-          <cell r="I42">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="A43">
-            <v>46142</v>
-          </cell>
-          <cell r="B43">
-            <v>0</v>
-          </cell>
-          <cell r="C43">
-            <v>2</v>
-          </cell>
-          <cell r="D43">
-            <v>0</v>
-          </cell>
-          <cell r="E43">
-            <v>2</v>
-          </cell>
-          <cell r="F43">
-            <v>0</v>
-          </cell>
-          <cell r="G43">
-            <v>0</v>
-          </cell>
-          <cell r="H43">
-            <v>0</v>
-          </cell>
-          <cell r="I43">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="A44">
-            <v>46143</v>
-          </cell>
-          <cell r="B44">
-            <v>0</v>
-          </cell>
-          <cell r="C44">
-            <v>2</v>
-          </cell>
-          <cell r="D44">
-            <v>0</v>
-          </cell>
-          <cell r="E44">
-            <v>2</v>
-          </cell>
-          <cell r="F44">
-            <v>0</v>
-          </cell>
-          <cell r="G44">
-            <v>0</v>
-          </cell>
-          <cell r="H44">
-            <v>0</v>
-          </cell>
-          <cell r="I44">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="A45">
-            <v>46144</v>
-          </cell>
-          <cell r="B45">
-            <v>0</v>
-          </cell>
-          <cell r="C45">
-            <v>2</v>
-          </cell>
-          <cell r="D45">
-            <v>0</v>
-          </cell>
-          <cell r="E45">
-            <v>2</v>
-          </cell>
-          <cell r="F45">
-            <v>0</v>
-          </cell>
-          <cell r="G45">
-            <v>0</v>
-          </cell>
-          <cell r="H45">
-            <v>0</v>
-          </cell>
-          <cell r="I45">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="A46">
-            <v>46145</v>
-          </cell>
-          <cell r="B46">
-            <v>0</v>
-          </cell>
-          <cell r="C46">
-            <v>2</v>
-          </cell>
-          <cell r="D46">
-            <v>0</v>
-          </cell>
-          <cell r="E46">
-            <v>2</v>
-          </cell>
-          <cell r="F46">
-            <v>0</v>
-          </cell>
-          <cell r="G46">
-            <v>0</v>
-          </cell>
-          <cell r="H46">
-            <v>0</v>
-          </cell>
-          <cell r="I46">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="A47">
-            <v>46146</v>
-          </cell>
-          <cell r="B47">
-            <v>1</v>
-          </cell>
-          <cell r="C47">
-            <v>3</v>
-          </cell>
-          <cell r="D47">
-            <v>1</v>
-          </cell>
-          <cell r="E47">
-            <v>3</v>
-          </cell>
-          <cell r="F47">
-            <v>0</v>
-          </cell>
-          <cell r="G47">
-            <v>0</v>
-          </cell>
-          <cell r="H47">
-            <v>0</v>
-          </cell>
-          <cell r="I47">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="A48">
-            <v>46147</v>
-          </cell>
-          <cell r="B48">
-            <v>0</v>
-          </cell>
-          <cell r="C48">
-            <v>3</v>
-          </cell>
-          <cell r="D48">
-            <v>0</v>
-          </cell>
-          <cell r="E48">
-            <v>3</v>
-          </cell>
-          <cell r="F48">
-            <v>0</v>
-          </cell>
-          <cell r="G48">
-            <v>0</v>
-          </cell>
-          <cell r="H48">
-            <v>0</v>
-          </cell>
-          <cell r="I48">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="A49">
-            <v>46148</v>
-          </cell>
-          <cell r="B49">
-            <v>0</v>
-          </cell>
-          <cell r="C49">
-            <v>3</v>
-          </cell>
-          <cell r="D49">
-            <v>0</v>
-          </cell>
-          <cell r="E49">
-            <v>3</v>
-          </cell>
-          <cell r="F49">
-            <v>0</v>
-          </cell>
-          <cell r="G49">
-            <v>0</v>
-          </cell>
-          <cell r="H49">
-            <v>0</v>
-          </cell>
-          <cell r="I49">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="A50">
-            <v>46149</v>
-          </cell>
-          <cell r="B50">
-            <v>0</v>
-          </cell>
-          <cell r="C50">
-            <v>3</v>
-          </cell>
-          <cell r="D50">
-            <v>0</v>
-          </cell>
-          <cell r="E50">
-            <v>3</v>
-          </cell>
-          <cell r="F50">
-            <v>0</v>
-          </cell>
-          <cell r="G50">
-            <v>0</v>
-          </cell>
-          <cell r="H50">
-            <v>0</v>
-          </cell>
-          <cell r="I50">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="A51">
-            <v>46150</v>
-          </cell>
-          <cell r="B51">
-            <v>0</v>
-          </cell>
-          <cell r="C51">
-            <v>3</v>
-          </cell>
-          <cell r="D51">
-            <v>0</v>
-          </cell>
-          <cell r="E51">
-            <v>3</v>
-          </cell>
-          <cell r="F51">
-            <v>0</v>
-          </cell>
-          <cell r="G51">
-            <v>0</v>
-          </cell>
-          <cell r="H51">
-            <v>0</v>
-          </cell>
-          <cell r="I51">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="A52">
-            <v>46151</v>
-          </cell>
-          <cell r="B52">
-            <v>0</v>
-          </cell>
-          <cell r="C52">
-            <v>3</v>
-          </cell>
-          <cell r="D52">
-            <v>0</v>
-          </cell>
-          <cell r="E52">
-            <v>3</v>
-          </cell>
-          <cell r="F52">
-            <v>0</v>
-          </cell>
-          <cell r="G52">
-            <v>0</v>
-          </cell>
-          <cell r="H52">
-            <v>0</v>
-          </cell>
-          <cell r="I52">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="A53">
-            <v>46152</v>
-          </cell>
-          <cell r="B53">
-            <v>0</v>
-          </cell>
-          <cell r="C53">
-            <v>3</v>
-          </cell>
-          <cell r="D53">
-            <v>0</v>
-          </cell>
-          <cell r="E53">
-            <v>3</v>
-          </cell>
-          <cell r="F53">
-            <v>0</v>
-          </cell>
-          <cell r="G53">
-            <v>0</v>
-          </cell>
-          <cell r="H53">
-            <v>0</v>
-          </cell>
-          <cell r="I53">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="A54">
-            <v>46153</v>
-          </cell>
-          <cell r="B54">
-            <v>0</v>
-          </cell>
-          <cell r="C54">
-            <v>3</v>
-          </cell>
-          <cell r="D54">
-            <v>0</v>
-          </cell>
-          <cell r="E54">
-            <v>3</v>
-          </cell>
-          <cell r="F54">
-            <v>0</v>
-          </cell>
-          <cell r="G54">
-            <v>0</v>
-          </cell>
-          <cell r="H54">
-            <v>0</v>
-          </cell>
-          <cell r="I54">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="A55">
-            <v>46154</v>
-          </cell>
-          <cell r="B55">
-            <v>0</v>
-          </cell>
-          <cell r="C55">
-            <v>3</v>
-          </cell>
-          <cell r="D55">
-            <v>0</v>
-          </cell>
-          <cell r="E55">
-            <v>3</v>
-          </cell>
-          <cell r="F55">
-            <v>0</v>
-          </cell>
-          <cell r="G55">
-            <v>0</v>
-          </cell>
-          <cell r="H55">
-            <v>0</v>
-          </cell>
-          <cell r="I55">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="A56">
-            <v>46155</v>
-          </cell>
-          <cell r="B56">
-            <v>0</v>
-          </cell>
-          <cell r="C56">
-            <v>3</v>
-          </cell>
-          <cell r="D56">
-            <v>0</v>
-          </cell>
-          <cell r="E56">
-            <v>3</v>
-          </cell>
-          <cell r="F56">
-            <v>0</v>
-          </cell>
-          <cell r="G56">
-            <v>0</v>
-          </cell>
-          <cell r="H56">
-            <v>0</v>
-          </cell>
-          <cell r="I56">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="A57">
-            <v>46156</v>
-          </cell>
-          <cell r="B57">
-            <v>0</v>
-          </cell>
-          <cell r="C57">
-            <v>3</v>
-          </cell>
-          <cell r="D57">
-            <v>0</v>
-          </cell>
-          <cell r="E57">
-            <v>3</v>
-          </cell>
-          <cell r="F57">
-            <v>0</v>
-          </cell>
-          <cell r="G57">
-            <v>0</v>
-          </cell>
-          <cell r="H57">
-            <v>0</v>
-          </cell>
-          <cell r="I57">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="A58">
-            <v>46157</v>
-          </cell>
-          <cell r="B58">
-            <v>0</v>
-          </cell>
-          <cell r="C58">
-            <v>3</v>
-          </cell>
-          <cell r="D58">
-            <v>0</v>
-          </cell>
-          <cell r="E58">
-            <v>3</v>
-          </cell>
-          <cell r="F58">
-            <v>0</v>
-          </cell>
-          <cell r="G58">
-            <v>0</v>
-          </cell>
-          <cell r="H58">
-            <v>0</v>
-          </cell>
-          <cell r="I58">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="A59">
-            <v>46158</v>
-          </cell>
-          <cell r="B59">
-            <v>0</v>
-          </cell>
-          <cell r="C59">
-            <v>3</v>
-          </cell>
-          <cell r="D59">
-            <v>0</v>
-          </cell>
-          <cell r="E59">
-            <v>3</v>
-          </cell>
-          <cell r="F59">
-            <v>0</v>
-          </cell>
-          <cell r="G59">
-            <v>0</v>
-          </cell>
-          <cell r="H59">
-            <v>0</v>
-          </cell>
-          <cell r="I59">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="A60">
-            <v>46159</v>
-          </cell>
-          <cell r="B60">
-            <v>0</v>
-          </cell>
-          <cell r="C60">
-            <v>3</v>
-          </cell>
-          <cell r="D60">
-            <v>0</v>
-          </cell>
-          <cell r="E60">
-            <v>3</v>
-          </cell>
-          <cell r="F60">
-            <v>0</v>
-          </cell>
-          <cell r="G60">
-            <v>0</v>
-          </cell>
-          <cell r="H60">
-            <v>0</v>
-          </cell>
-          <cell r="I60">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="A61">
-            <v>46160</v>
-          </cell>
-          <cell r="B61">
-            <v>0</v>
-          </cell>
-          <cell r="C61">
-            <v>3</v>
-          </cell>
-          <cell r="D61">
-            <v>0</v>
-          </cell>
-          <cell r="E61">
-            <v>3</v>
-          </cell>
-          <cell r="F61">
-            <v>0</v>
-          </cell>
-          <cell r="G61">
-            <v>0</v>
-          </cell>
-          <cell r="H61">
-            <v>0</v>
-          </cell>
-          <cell r="I61">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="A62">
-            <v>46161</v>
-          </cell>
-          <cell r="B62">
-            <v>1</v>
-          </cell>
-          <cell r="C62">
-            <v>4</v>
-          </cell>
-          <cell r="D62">
-            <v>0</v>
-          </cell>
-          <cell r="E62">
-            <v>3</v>
-          </cell>
-          <cell r="F62">
-            <v>2</v>
-          </cell>
-          <cell r="G62">
-            <v>0</v>
-          </cell>
-          <cell r="H62">
-            <v>2</v>
-          </cell>
-          <cell r="I62">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="A63">
-            <v>46162</v>
-          </cell>
-          <cell r="B63">
-            <v>1</v>
-          </cell>
-          <cell r="C63">
-            <v>5</v>
-          </cell>
-          <cell r="D63">
-            <v>0</v>
-          </cell>
-          <cell r="E63">
-            <v>3</v>
-          </cell>
-          <cell r="F63">
-            <v>0</v>
-          </cell>
-          <cell r="G63">
-            <v>0</v>
-          </cell>
-          <cell r="H63">
-            <v>2</v>
-          </cell>
-          <cell r="I63">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="A64">
-            <v>46163</v>
-          </cell>
-          <cell r="B64">
-            <v>4</v>
-          </cell>
-          <cell r="C64">
-            <v>9</v>
-          </cell>
-          <cell r="D64">
-            <v>0</v>
-          </cell>
-          <cell r="E64">
-            <v>3</v>
-          </cell>
-          <cell r="F64">
-            <v>0</v>
-          </cell>
-          <cell r="G64">
-            <v>0</v>
-          </cell>
-          <cell r="H64">
-            <v>2</v>
-          </cell>
-          <cell r="I64">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="A65">
-            <v>46164</v>
-          </cell>
-          <cell r="B65">
-            <v>0</v>
-          </cell>
-          <cell r="C65">
-            <v>9</v>
-          </cell>
-          <cell r="D65">
-            <v>0</v>
-          </cell>
-          <cell r="E65">
-            <v>3</v>
-          </cell>
-          <cell r="F65">
-            <v>0</v>
-          </cell>
-          <cell r="G65">
-            <v>0</v>
-          </cell>
-          <cell r="H65">
-            <v>2</v>
-          </cell>
-          <cell r="I65">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="A66">
-            <v>46165</v>
-          </cell>
-          <cell r="B66">
-            <v>0</v>
-          </cell>
-          <cell r="C66">
-            <v>9</v>
-          </cell>
-          <cell r="D66">
-            <v>0</v>
-          </cell>
-          <cell r="E66">
-            <v>3</v>
-          </cell>
-          <cell r="F66">
-            <v>0</v>
-          </cell>
-          <cell r="G66">
-            <v>0</v>
-          </cell>
-          <cell r="H66">
-            <v>2</v>
-          </cell>
-          <cell r="I66">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="A67">
-            <v>46166</v>
-          </cell>
-          <cell r="B67">
-            <v>0</v>
-          </cell>
-          <cell r="C67">
-            <v>9</v>
-          </cell>
-          <cell r="D67">
-            <v>0</v>
-          </cell>
-          <cell r="E67">
-            <v>3</v>
-          </cell>
-          <cell r="F67">
-            <v>0</v>
-          </cell>
-          <cell r="G67">
-            <v>0</v>
-          </cell>
-          <cell r="H67">
-            <v>2</v>
-          </cell>
-          <cell r="I67">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="A68">
-            <v>46167</v>
-          </cell>
-          <cell r="B68">
-            <v>1</v>
-          </cell>
-          <cell r="C68">
-            <v>10</v>
-          </cell>
-          <cell r="D68">
-            <v>0</v>
-          </cell>
-          <cell r="E68">
-            <v>3</v>
-          </cell>
-          <cell r="F68">
-            <v>1</v>
-          </cell>
-          <cell r="G68">
-            <v>0</v>
-          </cell>
-          <cell r="H68">
-            <v>3</v>
-          </cell>
-          <cell r="I68">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="A69">
-            <v>46168</v>
-          </cell>
-          <cell r="B69">
-            <v>2</v>
-          </cell>
-          <cell r="C69">
-            <v>12</v>
-          </cell>
-          <cell r="D69">
-            <v>1</v>
-          </cell>
-          <cell r="E69">
-            <v>4</v>
-          </cell>
-          <cell r="F69">
-            <v>1</v>
-          </cell>
-          <cell r="G69">
-            <v>0</v>
-          </cell>
-          <cell r="H69">
-            <v>4</v>
-          </cell>
-          <cell r="I69">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="A70">
-            <v>46169</v>
-          </cell>
-          <cell r="B70">
-            <v>1</v>
-          </cell>
-          <cell r="C70">
-            <v>13</v>
-          </cell>
-          <cell r="D70">
-            <v>1</v>
-          </cell>
-          <cell r="E70">
-            <v>5</v>
-          </cell>
-          <cell r="F70">
-            <v>4</v>
-          </cell>
-          <cell r="G70">
-            <v>0</v>
-          </cell>
-          <cell r="H70">
-            <v>8</v>
-          </cell>
-          <cell r="I70">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="A71">
-            <v>46170</v>
-          </cell>
-          <cell r="B71">
-            <v>1</v>
-          </cell>
-          <cell r="C71">
-            <v>14</v>
-          </cell>
-          <cell r="D71">
-            <v>0</v>
-          </cell>
-          <cell r="E71">
-            <v>5</v>
-          </cell>
-          <cell r="F71">
-            <v>0</v>
-          </cell>
-          <cell r="G71">
-            <v>1</v>
-          </cell>
-          <cell r="H71">
-            <v>8</v>
-          </cell>
-          <cell r="I71">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="A72">
-            <v>46171</v>
-          </cell>
-          <cell r="B72">
-            <v>0</v>
-          </cell>
-          <cell r="C72">
-            <v>14</v>
-          </cell>
-          <cell r="D72">
-            <v>1</v>
-          </cell>
-          <cell r="E72">
-            <v>6</v>
-          </cell>
-          <cell r="F72">
-            <v>1</v>
-          </cell>
-          <cell r="G72">
-            <v>0</v>
-          </cell>
-          <cell r="H72">
-            <v>9</v>
-          </cell>
-          <cell r="I72">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="A73">
-            <v>46172</v>
-          </cell>
-          <cell r="B73">
-            <v>0</v>
-          </cell>
-          <cell r="C73">
-            <v>14</v>
-          </cell>
-          <cell r="D73">
-            <v>0</v>
-          </cell>
-          <cell r="E73">
-            <v>6</v>
-          </cell>
-          <cell r="F73">
-            <v>0</v>
-          </cell>
-          <cell r="G73">
-            <v>0</v>
-          </cell>
-          <cell r="H73">
-            <v>9</v>
-          </cell>
-          <cell r="I73">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="A74">
-            <v>46173</v>
-          </cell>
-          <cell r="B74">
-            <v>0</v>
-          </cell>
-          <cell r="C74">
-            <v>14</v>
-          </cell>
-          <cell r="D74">
-            <v>0</v>
-          </cell>
-          <cell r="E74">
-            <v>6</v>
-          </cell>
-          <cell r="F74">
-            <v>0</v>
-          </cell>
-          <cell r="G74">
-            <v>0</v>
-          </cell>
-          <cell r="H74">
-            <v>9</v>
-          </cell>
-          <cell r="I74">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="A75">
-            <v>46174</v>
-          </cell>
-          <cell r="B75">
-            <v>2</v>
-          </cell>
-          <cell r="C75">
-            <v>16</v>
-          </cell>
-          <cell r="D75">
-            <v>0</v>
-          </cell>
-          <cell r="E75">
-            <v>6</v>
-          </cell>
-          <cell r="F75">
-            <v>1</v>
-          </cell>
-          <cell r="G75">
-            <v>1</v>
-          </cell>
-          <cell r="H75">
-            <v>10</v>
-          </cell>
-          <cell r="I75">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="A76">
-            <v>46175</v>
-          </cell>
-          <cell r="B76">
-            <v>0</v>
-          </cell>
-          <cell r="C76">
-            <v>16</v>
-          </cell>
-          <cell r="D76">
-            <v>0</v>
-          </cell>
-          <cell r="E76">
-            <v>6</v>
-          </cell>
-          <cell r="F76">
-            <v>1</v>
-          </cell>
-          <cell r="G76">
-            <v>1</v>
-          </cell>
-          <cell r="H76">
-            <v>11</v>
-          </cell>
-          <cell r="I76">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="77">
-          <cell r="A77">
-            <v>46176</v>
-          </cell>
-          <cell r="B77">
-            <v>0</v>
-          </cell>
-          <cell r="C77">
-            <v>16</v>
-          </cell>
-          <cell r="D77">
-            <v>1</v>
-          </cell>
-          <cell r="E77">
-            <v>7</v>
-          </cell>
-          <cell r="F77">
-            <v>2</v>
-          </cell>
-          <cell r="G77">
-            <v>0</v>
-          </cell>
-          <cell r="H77">
-            <v>13</v>
-          </cell>
-          <cell r="I77">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="78">
-          <cell r="A78">
-            <v>46177</v>
-          </cell>
-          <cell r="B78">
-            <v>7</v>
-          </cell>
-          <cell r="C78">
-            <v>23</v>
-          </cell>
-          <cell r="D78">
-            <v>0</v>
-          </cell>
-          <cell r="E78">
-            <v>7</v>
-          </cell>
-          <cell r="F78">
-            <v>0</v>
-          </cell>
-          <cell r="G78">
-            <v>0</v>
-          </cell>
-          <cell r="H78">
-            <v>13</v>
-          </cell>
-          <cell r="I78">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="79">
-          <cell r="A79">
-            <v>46178</v>
-          </cell>
-          <cell r="B79">
-            <v>0</v>
-          </cell>
-          <cell r="C79">
-            <v>23</v>
-          </cell>
-          <cell r="D79">
-            <v>0</v>
-          </cell>
-          <cell r="E79">
-            <v>7</v>
-          </cell>
-          <cell r="F79">
-            <v>2</v>
-          </cell>
-          <cell r="G79">
-            <v>0</v>
-          </cell>
-          <cell r="H79">
-            <v>15</v>
-          </cell>
-          <cell r="I79">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="80">
-          <cell r="A80">
-            <v>46179</v>
-          </cell>
-          <cell r="B80">
-            <v>0</v>
-          </cell>
-          <cell r="C80">
-            <v>23</v>
-          </cell>
-          <cell r="D80">
-            <v>0</v>
-          </cell>
-          <cell r="E80">
-            <v>7</v>
-          </cell>
-          <cell r="F80">
-            <v>0</v>
-          </cell>
-          <cell r="G80">
-            <v>0</v>
-          </cell>
-          <cell r="H80">
-            <v>15</v>
-          </cell>
-          <cell r="I80">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="81">
-          <cell r="A81">
-            <v>46180</v>
-          </cell>
-          <cell r="B81">
-            <v>0</v>
-          </cell>
-          <cell r="C81">
-            <v>23</v>
-          </cell>
-          <cell r="D81">
-            <v>0</v>
-          </cell>
-          <cell r="E81">
-            <v>7</v>
-          </cell>
-          <cell r="F81">
-            <v>0</v>
-          </cell>
-          <cell r="G81">
-            <v>0</v>
-          </cell>
-          <cell r="H81">
-            <v>15</v>
-          </cell>
-          <cell r="I81">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="82">
-          <cell r="A82">
-            <v>46181</v>
-          </cell>
-          <cell r="B82">
-            <v>0</v>
-          </cell>
-          <cell r="C82">
-            <v>23</v>
-          </cell>
-          <cell r="D82">
-            <v>0</v>
-          </cell>
-          <cell r="E82">
-            <v>7</v>
-          </cell>
-          <cell r="F82">
-            <v>0</v>
-          </cell>
-          <cell r="G82">
-            <v>0</v>
-          </cell>
-          <cell r="H82">
-            <v>15</v>
-          </cell>
-          <cell r="I82">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="83">
-          <cell r="A83">
-            <v>46182</v>
-          </cell>
-          <cell r="B83">
-            <v>8</v>
-          </cell>
-          <cell r="C83">
-            <v>31</v>
-          </cell>
-          <cell r="D83">
-            <v>0</v>
-          </cell>
-          <cell r="E83">
-            <v>7</v>
-          </cell>
-          <cell r="F83">
-            <v>0</v>
-          </cell>
-          <cell r="G83">
-            <v>0</v>
-          </cell>
-          <cell r="H83">
-            <v>15</v>
-          </cell>
-          <cell r="I83">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="84">
-          <cell r="A84">
-            <v>46183</v>
-          </cell>
-          <cell r="B84">
-            <v>0</v>
-          </cell>
-          <cell r="C84">
-            <v>31</v>
-          </cell>
-          <cell r="D84">
-            <v>0</v>
-          </cell>
-          <cell r="E84">
-            <v>7</v>
-          </cell>
-          <cell r="F84">
-            <v>7</v>
-          </cell>
-          <cell r="G84">
-            <v>0</v>
-          </cell>
-          <cell r="H84">
-            <v>22</v>
-          </cell>
-          <cell r="I84">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="85">
-          <cell r="A85">
-            <v>46184</v>
-          </cell>
-          <cell r="B85">
-            <v>1</v>
-          </cell>
-          <cell r="C85">
-            <v>32</v>
-          </cell>
-          <cell r="D85">
-            <v>0</v>
-          </cell>
-          <cell r="E85">
-            <v>7</v>
-          </cell>
-          <cell r="F85">
-            <v>0</v>
-          </cell>
-          <cell r="G85">
-            <v>0</v>
-          </cell>
-          <cell r="H85">
-            <v>22</v>
-          </cell>
-          <cell r="I85">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="86">
-          <cell r="A86">
-            <v>46185</v>
-          </cell>
-          <cell r="B86">
-            <v>2</v>
-          </cell>
-          <cell r="C86">
-            <v>34</v>
-          </cell>
-          <cell r="D86">
-            <v>4</v>
-          </cell>
-          <cell r="E86">
-            <v>11</v>
-          </cell>
-          <cell r="F86">
-            <v>0</v>
-          </cell>
-          <cell r="G86">
-            <v>0</v>
-          </cell>
-          <cell r="H86">
-            <v>22</v>
-          </cell>
-          <cell r="I86">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="87">
-          <cell r="A87">
-            <v>46186</v>
-          </cell>
-          <cell r="B87">
-            <v>0</v>
-          </cell>
-          <cell r="C87">
-            <v>34</v>
-          </cell>
-          <cell r="D87">
-            <v>0</v>
-          </cell>
-          <cell r="E87">
-            <v>11</v>
-          </cell>
-          <cell r="F87">
-            <v>0</v>
-          </cell>
-          <cell r="G87">
-            <v>0</v>
-          </cell>
-          <cell r="H87">
-            <v>22</v>
-          </cell>
-          <cell r="I87">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="88">
-          <cell r="A88">
-            <v>46187</v>
-          </cell>
-          <cell r="B88">
-            <v>0</v>
-          </cell>
-          <cell r="C88">
-            <v>34</v>
-          </cell>
-          <cell r="D88">
-            <v>0</v>
-          </cell>
-          <cell r="E88">
-            <v>11</v>
-          </cell>
-          <cell r="F88">
-            <v>0</v>
-          </cell>
-          <cell r="G88">
-            <v>0</v>
-          </cell>
-          <cell r="H88">
-            <v>22</v>
-          </cell>
-          <cell r="I88">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="89">
-          <cell r="A89">
-            <v>46188</v>
-          </cell>
-          <cell r="B89">
-            <v>0</v>
-          </cell>
-          <cell r="C89">
-            <v>34</v>
-          </cell>
-          <cell r="D89">
-            <v>0</v>
-          </cell>
-          <cell r="E89">
-            <v>11</v>
-          </cell>
-          <cell r="F89">
-            <v>8</v>
-          </cell>
-          <cell r="G89">
-            <v>0</v>
-          </cell>
-          <cell r="H89">
-            <v>30</v>
-          </cell>
-          <cell r="I89">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="90">
-          <cell r="A90">
-            <v>46189</v>
-          </cell>
-          <cell r="B90">
-            <v>6</v>
-          </cell>
-          <cell r="C90">
-            <v>40</v>
-          </cell>
-          <cell r="D90">
-            <v>4</v>
-          </cell>
-          <cell r="E90">
-            <v>15</v>
-          </cell>
-          <cell r="F90">
-            <v>1</v>
-          </cell>
-          <cell r="G90">
-            <v>0</v>
-          </cell>
-          <cell r="H90">
-            <v>31</v>
-          </cell>
-          <cell r="I90">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="91">
-          <cell r="A91">
-            <v>46190</v>
-          </cell>
-          <cell r="B91">
-            <v>0</v>
-          </cell>
-          <cell r="C91">
-            <v>40</v>
-          </cell>
-          <cell r="D91">
-            <v>0</v>
-          </cell>
-          <cell r="E91">
-            <v>15</v>
-          </cell>
-          <cell r="F91">
-            <v>1</v>
-          </cell>
-          <cell r="G91">
-            <v>0</v>
-          </cell>
-          <cell r="H91">
-            <v>32</v>
-          </cell>
-          <cell r="I91">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="92">
-          <cell r="A92">
-            <v>46191</v>
-          </cell>
-          <cell r="B92">
-            <v>0</v>
-          </cell>
-          <cell r="C92">
-            <v>40</v>
-          </cell>
-          <cell r="D92">
-            <v>1</v>
-          </cell>
-          <cell r="E92">
-            <v>16</v>
-          </cell>
-          <cell r="F92">
-            <v>2</v>
-          </cell>
-          <cell r="G92">
-            <v>0</v>
-          </cell>
-          <cell r="H92">
-            <v>34</v>
-          </cell>
-          <cell r="I92">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="93">
-          <cell r="A93">
-            <v>46192</v>
-          </cell>
-          <cell r="B93">
-            <v>2</v>
-          </cell>
-          <cell r="C93">
-            <v>42</v>
-          </cell>
-          <cell r="D93">
-            <v>3</v>
-          </cell>
-          <cell r="E93">
-            <v>19</v>
-          </cell>
-          <cell r="F93">
-            <v>0</v>
-          </cell>
-          <cell r="G93">
-            <v>0</v>
-          </cell>
-          <cell r="H93">
-            <v>34</v>
-          </cell>
-          <cell r="I93">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="94">
-          <cell r="A94">
-            <v>46193</v>
-          </cell>
-          <cell r="B94">
-            <v>0</v>
-          </cell>
-          <cell r="C94">
-            <v>42</v>
-          </cell>
-          <cell r="D94">
-            <v>0</v>
-          </cell>
-          <cell r="E94">
-            <v>19</v>
-          </cell>
-          <cell r="F94">
-            <v>0</v>
-          </cell>
-          <cell r="G94">
-            <v>0</v>
-          </cell>
-          <cell r="H94">
-            <v>34</v>
-          </cell>
-          <cell r="I94">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="95">
-          <cell r="A95">
-            <v>46194</v>
-          </cell>
-          <cell r="B95">
-            <v>0</v>
-          </cell>
-          <cell r="C95">
-            <v>42</v>
-          </cell>
-          <cell r="D95">
-            <v>0</v>
-          </cell>
-          <cell r="E95">
-            <v>19</v>
-          </cell>
-          <cell r="F95">
-            <v>0</v>
-          </cell>
-          <cell r="G95">
-            <v>0</v>
-          </cell>
-          <cell r="H95">
-            <v>34</v>
-          </cell>
-          <cell r="I95">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="96">
-          <cell r="A96">
-            <v>46195</v>
-          </cell>
-          <cell r="B96">
-            <v>1</v>
-          </cell>
-          <cell r="C96">
-            <v>43</v>
-          </cell>
-          <cell r="D96">
-            <v>0</v>
-          </cell>
-          <cell r="E96">
-            <v>19</v>
-          </cell>
-          <cell r="F96">
-            <v>6</v>
-          </cell>
-          <cell r="G96">
-            <v>0</v>
-          </cell>
-          <cell r="H96">
-            <v>40</v>
-          </cell>
-          <cell r="I96">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="97">
-          <cell r="A97">
-            <v>46196</v>
-          </cell>
-          <cell r="B97">
-            <v>6</v>
-          </cell>
-          <cell r="C97">
-            <v>49</v>
-          </cell>
-          <cell r="D97">
-            <v>11</v>
-          </cell>
-          <cell r="E97">
-            <v>30</v>
-          </cell>
-          <cell r="F97">
-            <v>0</v>
-          </cell>
-          <cell r="G97">
-            <v>0</v>
-          </cell>
-          <cell r="H97">
-            <v>40</v>
-          </cell>
-          <cell r="I97">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="98">
-          <cell r="A98">
-            <v>46197</v>
-          </cell>
-          <cell r="B98">
-            <v>0</v>
-          </cell>
-          <cell r="C98">
-            <v>49</v>
-          </cell>
-          <cell r="D98">
-            <v>9</v>
-          </cell>
-          <cell r="E98">
-            <v>39</v>
-          </cell>
-          <cell r="F98">
-            <v>0</v>
-          </cell>
-          <cell r="G98">
-            <v>0</v>
-          </cell>
-          <cell r="H98">
-            <v>40</v>
-          </cell>
-          <cell r="I98">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="99">
-          <cell r="A99">
-            <v>46198</v>
-          </cell>
-          <cell r="B99">
-            <v>2</v>
-          </cell>
-          <cell r="C99">
-            <v>51</v>
-          </cell>
-          <cell r="D99">
-            <v>1</v>
-          </cell>
-          <cell r="E99">
-            <v>40</v>
-          </cell>
-          <cell r="F99">
-            <v>2</v>
-          </cell>
-          <cell r="G99">
-            <v>0</v>
-          </cell>
-          <cell r="H99">
-            <v>42</v>
-          </cell>
-          <cell r="I99">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="100">
-          <cell r="A100">
-            <v>46199</v>
-          </cell>
-          <cell r="B100">
-            <v>0</v>
-          </cell>
-          <cell r="C100">
-            <v>51</v>
-          </cell>
-          <cell r="D100">
-            <v>4</v>
-          </cell>
-          <cell r="E100">
-            <v>44</v>
-          </cell>
-          <cell r="F100">
-            <v>7</v>
-          </cell>
-          <cell r="G100">
-            <v>0</v>
-          </cell>
-          <cell r="H100">
-            <v>49</v>
-          </cell>
-          <cell r="I100">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="101">
-          <cell r="A101">
-            <v>46200</v>
-          </cell>
-          <cell r="B101">
-            <v>0</v>
-          </cell>
-          <cell r="C101">
-            <v>51</v>
-          </cell>
-          <cell r="D101">
-            <v>0</v>
-          </cell>
-          <cell r="E101">
-            <v>44</v>
-          </cell>
-          <cell r="F101">
-            <v>0</v>
-          </cell>
-          <cell r="G101">
-            <v>0</v>
-          </cell>
-          <cell r="H101">
-            <v>49</v>
-          </cell>
-          <cell r="I101">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="102">
-          <cell r="A102">
-            <v>46201</v>
-          </cell>
-          <cell r="B102">
-            <v>0</v>
-          </cell>
-          <cell r="C102">
-            <v>51</v>
-          </cell>
-          <cell r="D102">
-            <v>0</v>
-          </cell>
-          <cell r="E102">
-            <v>44</v>
-          </cell>
-          <cell r="F102">
-            <v>0</v>
-          </cell>
-          <cell r="G102">
-            <v>0</v>
-          </cell>
-          <cell r="H102">
-            <v>49</v>
-          </cell>
-          <cell r="I102">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="103">
-          <cell r="A103">
-            <v>46202</v>
-          </cell>
-          <cell r="B103">
-            <v>3</v>
-          </cell>
-          <cell r="C103">
-            <v>54</v>
-          </cell>
-          <cell r="D103">
-            <v>4</v>
-          </cell>
-          <cell r="E103">
-            <v>48</v>
-          </cell>
-          <cell r="F103">
-            <v>0</v>
-          </cell>
-          <cell r="G103">
-            <v>0</v>
-          </cell>
-          <cell r="H103">
-            <v>49</v>
-          </cell>
-          <cell r="I103">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="104">
-          <cell r="A104">
-            <v>46203</v>
-          </cell>
-          <cell r="B104">
-            <v>3</v>
-          </cell>
-          <cell r="C104">
-            <v>57</v>
-          </cell>
-          <cell r="D104">
-            <v>0</v>
-          </cell>
-          <cell r="E104">
-            <v>48</v>
-          </cell>
-          <cell r="F104">
-            <v>0</v>
-          </cell>
-          <cell r="G104">
-            <v>0</v>
-          </cell>
-          <cell r="H104">
-            <v>49</v>
-          </cell>
-          <cell r="I104">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="105">
-          <cell r="A105">
-            <v>46204</v>
-          </cell>
-          <cell r="B105">
-            <v>22</v>
-          </cell>
-          <cell r="C105">
-            <v>79</v>
-          </cell>
-          <cell r="D105">
-            <v>6</v>
-          </cell>
-          <cell r="E105">
-            <v>54</v>
-          </cell>
-          <cell r="F105">
-            <v>2</v>
-          </cell>
-          <cell r="G105">
-            <v>0</v>
-          </cell>
-          <cell r="H105">
-            <v>51</v>
-          </cell>
-          <cell r="I105">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="106">
-          <cell r="A106">
-            <v>46205</v>
-          </cell>
-          <cell r="B106">
-            <v>22</v>
-          </cell>
-          <cell r="C106">
-            <v>101</v>
-          </cell>
-          <cell r="D106">
-            <v>1</v>
-          </cell>
-          <cell r="E106">
-            <v>55</v>
-          </cell>
-          <cell r="F106">
-            <v>3</v>
-          </cell>
-          <cell r="G106">
-            <v>0</v>
-          </cell>
-          <cell r="H106">
-            <v>54</v>
-          </cell>
-          <cell r="I106">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="107">
-          <cell r="A107">
-            <v>46206</v>
-          </cell>
-          <cell r="B107">
-            <v>1</v>
-          </cell>
-          <cell r="C107">
-            <v>102</v>
-          </cell>
-          <cell r="D107">
-            <v>6</v>
-          </cell>
-          <cell r="E107">
-            <v>61</v>
-          </cell>
-          <cell r="F107">
-            <v>0</v>
-          </cell>
-          <cell r="G107">
-            <v>0</v>
-          </cell>
-          <cell r="H107">
-            <v>54</v>
-          </cell>
-          <cell r="I107">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="108">
-          <cell r="A108">
-            <v>46207</v>
-          </cell>
-          <cell r="B108">
-            <v>0</v>
-          </cell>
-          <cell r="C108">
-            <v>102</v>
-          </cell>
-          <cell r="D108">
-            <v>0</v>
-          </cell>
-          <cell r="E108">
-            <v>61</v>
-          </cell>
-          <cell r="F108">
-            <v>0</v>
-          </cell>
-          <cell r="G108">
-            <v>0</v>
-          </cell>
-          <cell r="H108">
-            <v>54</v>
-          </cell>
-          <cell r="I108">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="109">
-          <cell r="A109">
-            <v>46208</v>
-          </cell>
-          <cell r="B109">
-            <v>0</v>
-          </cell>
-          <cell r="C109">
-            <v>102</v>
-          </cell>
-          <cell r="D109">
-            <v>0</v>
-          </cell>
-          <cell r="E109">
-            <v>61</v>
-          </cell>
-          <cell r="F109">
-            <v>0</v>
-          </cell>
-          <cell r="G109">
-            <v>0</v>
-          </cell>
-          <cell r="H109">
-            <v>54</v>
-          </cell>
-          <cell r="I109">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="110">
-          <cell r="A110">
-            <v>46209</v>
-          </cell>
-          <cell r="B110">
-            <v>0</v>
-          </cell>
-          <cell r="C110">
-            <v>102</v>
-          </cell>
-          <cell r="D110">
-            <v>0</v>
-          </cell>
-          <cell r="E110">
-            <v>61</v>
-          </cell>
-          <cell r="F110">
-            <v>3</v>
-          </cell>
-          <cell r="G110">
-            <v>0</v>
-          </cell>
-          <cell r="H110">
-            <v>57</v>
-          </cell>
-          <cell r="I110">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="111">
-          <cell r="A111">
-            <v>46210</v>
-          </cell>
-          <cell r="B111">
-            <v>0</v>
-          </cell>
-          <cell r="C111">
-            <v>102</v>
-          </cell>
-          <cell r="D111">
-            <v>0</v>
-          </cell>
-          <cell r="F111">
-            <v>22</v>
-          </cell>
-          <cell r="G111">
-            <v>0</v>
-          </cell>
-          <cell r="H111">
-            <v>79</v>
-          </cell>
-        </row>
-        <row r="112">
-          <cell r="A112">
-            <v>46211</v>
-          </cell>
-          <cell r="B112">
-            <v>3</v>
-          </cell>
-          <cell r="C112">
-            <v>105</v>
-          </cell>
-          <cell r="D112">
-            <v>0</v>
-          </cell>
-          <cell r="F112">
-            <v>22</v>
-          </cell>
-          <cell r="G112">
-            <v>0</v>
-          </cell>
-          <cell r="H112">
-            <v>101</v>
-          </cell>
-        </row>
-        <row r="113">
-          <cell r="A113">
-            <v>46212</v>
-          </cell>
-          <cell r="B113">
-            <v>0</v>
-          </cell>
-          <cell r="C113">
-            <v>105</v>
-          </cell>
-          <cell r="D113">
-            <v>0</v>
-          </cell>
-          <cell r="F113">
-            <v>0</v>
-          </cell>
-          <cell r="G113">
-            <v>0</v>
-          </cell>
-          <cell r="H113">
-            <v>101</v>
-          </cell>
-        </row>
-        <row r="114">
-          <cell r="A114">
-            <v>46213</v>
-          </cell>
-          <cell r="B114">
-            <v>0</v>
-          </cell>
-          <cell r="C114">
-            <v>105</v>
-          </cell>
-          <cell r="D114">
-            <v>0</v>
-          </cell>
-          <cell r="F114">
-            <v>0</v>
-          </cell>
-          <cell r="G114">
-            <v>0</v>
-          </cell>
-          <cell r="H114">
-            <v>101</v>
-          </cell>
-        </row>
-        <row r="115">
-          <cell r="A115">
-            <v>46214</v>
-          </cell>
-          <cell r="B115">
-            <v>0</v>
-          </cell>
-          <cell r="C115">
-            <v>105</v>
-          </cell>
-          <cell r="D115">
-            <v>0</v>
-          </cell>
-          <cell r="F115">
-            <v>0</v>
-          </cell>
-          <cell r="G115">
-            <v>0</v>
-          </cell>
-          <cell r="H115">
-            <v>101</v>
-          </cell>
-        </row>
-        <row r="116">
-          <cell r="A116">
-            <v>46215</v>
-          </cell>
-          <cell r="B116">
-            <v>0</v>
-          </cell>
-          <cell r="C116">
-            <v>105</v>
-          </cell>
-          <cell r="D116">
-            <v>0</v>
-          </cell>
-          <cell r="F116">
-            <v>0</v>
-          </cell>
-          <cell r="G116">
-            <v>0</v>
-          </cell>
-          <cell r="H116">
-            <v>101</v>
-          </cell>
-        </row>
-        <row r="117">
-          <cell r="A117">
-            <v>46216</v>
-          </cell>
-          <cell r="B117">
-            <v>0</v>
-          </cell>
-          <cell r="C117">
-            <v>105</v>
-          </cell>
-          <cell r="D117">
-            <v>0</v>
-          </cell>
-          <cell r="F117">
-            <v>1</v>
-          </cell>
-          <cell r="G117">
-            <v>0</v>
-          </cell>
-          <cell r="H117">
-            <v>102</v>
-          </cell>
-        </row>
-        <row r="118">
-          <cell r="A118">
-            <v>46217</v>
-          </cell>
-          <cell r="B118">
-            <v>0</v>
-          </cell>
-          <cell r="C118">
-            <v>105</v>
-          </cell>
-          <cell r="D118">
-            <v>0</v>
-          </cell>
-          <cell r="F118">
-            <v>0</v>
-          </cell>
-          <cell r="G118">
-            <v>0</v>
-          </cell>
-          <cell r="H118">
-            <v>102</v>
-          </cell>
-        </row>
-        <row r="119">
-          <cell r="A119">
-            <v>46218</v>
-          </cell>
-          <cell r="B119">
-            <v>0</v>
-          </cell>
-          <cell r="C119">
-            <v>105</v>
-          </cell>
-          <cell r="D119">
-            <v>0</v>
-          </cell>
-          <cell r="F119">
-            <v>0</v>
-          </cell>
-          <cell r="G119">
-            <v>0</v>
-          </cell>
-          <cell r="H119">
-            <v>102</v>
-          </cell>
-        </row>
-        <row r="120">
-          <cell r="A120">
-            <v>46219</v>
-          </cell>
-          <cell r="B120">
-            <v>0</v>
-          </cell>
-          <cell r="C120">
-            <v>105</v>
-          </cell>
-          <cell r="D120">
-            <v>0</v>
-          </cell>
-          <cell r="F120">
-            <v>3</v>
-          </cell>
-          <cell r="G120">
-            <v>0</v>
-          </cell>
-          <cell r="H120">
-            <v>105</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4BCB2CBC-7252-4609-A504-136211063410}" name="Tabela1" displayName="Tabela1" ref="A1:AF184" totalsRowShown="0" headerRowDxfId="135" dataDxfId="134">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4BCB2CBC-7252-4609-A504-136211063410}" name="Tabela1" displayName="Tabela1" ref="A1:AF184" totalsRowShown="0" headerRowDxfId="127" dataDxfId="126">
   <autoFilter ref="A1:AF184" xr:uid="{4BCB2CBC-7252-4609-A504-136211063410}"/>
   <tableColumns count="32">
-    <tableColumn id="1" xr3:uid="{9B6F1BF5-3176-4963-A2E7-9C3829CC1200}" name="Id" dataDxfId="160"/>
-    <tableColumn id="2" xr3:uid="{226B5D93-189B-4E78-8084-23089E590ABC}" name="EDT" dataDxfId="159"/>
-    <tableColumn id="3" xr3:uid="{C76175BA-BFB6-4220-90FF-B75D87D5D53E}" name="Nome do Resumo da Tarefa" dataDxfId="158"/>
-    <tableColumn id="4" xr3:uid="{D23BE556-7009-435E-8FA9-FCAD6BFAD8A4}" name="Nome da Tarefa" dataDxfId="157"/>
-    <tableColumn id="5" xr3:uid="{BE6B0D70-DECB-4B07-90E6-3FA86E9C1615}" name="Título" dataDxfId="156"/>
-    <tableColumn id="6" xr3:uid="{743F9FF2-3CAE-416B-AD0C-DED9BFE19CCF}" name="Duração" dataDxfId="133"/>
-    <tableColumn id="7" xr3:uid="{C83BC5A1-E922-4815-B3A5-790D6549648E}" name="Início" dataDxfId="132"/>
-    <tableColumn id="8" xr3:uid="{26EF96BA-F7E9-4476-A4E0-B5D84575262D}" name="Término" dataDxfId="130"/>
-    <tableColumn id="9" xr3:uid="{2416999C-4F99-410A-A56E-04D13B01863F}" name="Predecessoras" dataDxfId="131"/>
-    <tableColumn id="10" xr3:uid="{CF230A23-8FFD-42DF-9BD0-53BD641A47DE}" name="% concluída" dataDxfId="129"/>
-    <tableColumn id="11" xr3:uid="{879DFC7A-E43E-40F2-B9A1-55DF75182AE1}" name="Término real" dataDxfId="127"/>
-    <tableColumn id="12" xr3:uid="{ABE4CF5F-347F-4FF6-A4C4-C6FFB15B20DD}" name="Status" dataDxfId="128"/>
-    <tableColumn id="13" xr3:uid="{733CFA72-609A-40FA-9780-07526905CD7B}" name="Crítica" dataDxfId="155"/>
-    <tableColumn id="14" xr3:uid="{C61733D4-18B6-4571-A784-2EB78EEA38CD}" name="Disciplina" dataDxfId="154"/>
-    <tableColumn id="15" xr3:uid="{389D190B-EB55-4CAA-AC9D-5B8FA9A519AA}" name="Inicio_LB_R0" dataDxfId="153"/>
-    <tableColumn id="16" xr3:uid="{106C4044-D370-4038-910C-AB55A197C297}" name="Término_LB_R0" dataDxfId="152"/>
-    <tableColumn id="17" xr3:uid="{6E032648-7E26-4640-B25E-1D062FB90AC7}" name="Sprint" dataDxfId="151"/>
-    <tableColumn id="18" xr3:uid="{690C88D3-1752-4678-8FD4-5DD23108B482}" name="Sucessoras" dataDxfId="150"/>
-    <tableColumn id="19" xr3:uid="{969B9EAF-5B20-495C-88E9-5BE22ACC4024}" name="Comparação" dataDxfId="149"/>
-    <tableColumn id="20" xr3:uid="{D23B245E-A538-4C56-BC73-A2346908CA33}" name="Nomes dos recursos" dataDxfId="148"/>
-    <tableColumn id="21" xr3:uid="{69B56DDE-EDB5-44E3-94A0-9DF32D950B32}" name="pct_val" dataDxfId="147"/>
-    <tableColumn id="22" xr3:uid="{4EB66340-A596-4078-9017-F7D7652830E2}" name="Emissão inicial total" dataDxfId="146"/>
-    <tableColumn id="23" xr3:uid="{41BF6A69-0203-4C01-A6CA-CA19979B2D9D}" name="Emissão inicial concluída" dataDxfId="145"/>
-    <tableColumn id="24" xr3:uid="{8D89AA0A-45FB-47E7-869B-267B596308B1}" name="Emissão Inicial Atrasada" dataDxfId="144"/>
-    <tableColumn id="25" xr3:uid="{9267BD68-23A8-488D-8561-D745A3CB58A6}" name="Aprovação total" dataDxfId="143"/>
-    <tableColumn id="26" xr3:uid="{F6257027-3A28-4907-A379-AB63305CE26F}" name="Avaliação do cliente concluída" dataDxfId="142"/>
-    <tableColumn id="27" xr3:uid="{49084566-DCA6-4F4D-9941-4B6987B7E387}" name="Avaliação Cliente Atrasada" dataDxfId="141"/>
-    <tableColumn id="28" xr3:uid="{BB0306E9-45DB-4AFB-8ECB-C6841821B00F}" name="Atendimento de comentário concluído" dataDxfId="140"/>
-    <tableColumn id="29" xr3:uid="{9F17512D-AEC3-4AA8-BBD2-F52F88C92032}" name="Atendimento Atrasado" dataDxfId="139"/>
-    <tableColumn id="30" xr3:uid="{A28EC239-F3FF-4653-B0ED-7D2A7C9A4047}" name="Aprovação concluída" dataDxfId="138"/>
-    <tableColumn id="31" xr3:uid="{B9B113F3-6B5F-4B16-888C-C5909411106C}" name="Aprovação Atrasada" dataDxfId="137"/>
-    <tableColumn id="32" xr3:uid="{294E4172-9AEE-4190-A6BE-6A07E2931923}" name="Aderência" dataDxfId="136"/>
+    <tableColumn id="1" xr3:uid="{9B6F1BF5-3176-4963-A2E7-9C3829CC1200}" name="Id" dataDxfId="125"/>
+    <tableColumn id="2" xr3:uid="{226B5D93-189B-4E78-8084-23089E590ABC}" name="EDT" dataDxfId="124"/>
+    <tableColumn id="3" xr3:uid="{C76175BA-BFB6-4220-90FF-B75D87D5D53E}" name="Nome do Resumo da Tarefa" dataDxfId="123"/>
+    <tableColumn id="4" xr3:uid="{D23BE556-7009-435E-8FA9-FCAD6BFAD8A4}" name="Nome da Tarefa" dataDxfId="122"/>
+    <tableColumn id="5" xr3:uid="{BE6B0D70-DECB-4B07-90E6-3FA86E9C1615}" name="Título" dataDxfId="121"/>
+    <tableColumn id="6" xr3:uid="{743F9FF2-3CAE-416B-AD0C-DED9BFE19CCF}" name="Duração" dataDxfId="120"/>
+    <tableColumn id="7" xr3:uid="{C83BC5A1-E922-4815-B3A5-790D6549648E}" name="Início" dataDxfId="119"/>
+    <tableColumn id="8" xr3:uid="{26EF96BA-F7E9-4476-A4E0-B5D84575262D}" name="Término" dataDxfId="118"/>
+    <tableColumn id="9" xr3:uid="{2416999C-4F99-410A-A56E-04D13B01863F}" name="Predecessoras" dataDxfId="117"/>
+    <tableColumn id="10" xr3:uid="{CF230A23-8FFD-42DF-9BD0-53BD641A47DE}" name="% concluída" dataDxfId="116"/>
+    <tableColumn id="11" xr3:uid="{879DFC7A-E43E-40F2-B9A1-55DF75182AE1}" name="Término real" dataDxfId="115"/>
+    <tableColumn id="12" xr3:uid="{ABE4CF5F-347F-4FF6-A4C4-C6FFB15B20DD}" name="Status" dataDxfId="114"/>
+    <tableColumn id="13" xr3:uid="{733CFA72-609A-40FA-9780-07526905CD7B}" name="Crítica" dataDxfId="113"/>
+    <tableColumn id="14" xr3:uid="{C61733D4-18B6-4571-A784-2EB78EEA38CD}" name="Disciplina" dataDxfId="112"/>
+    <tableColumn id="15" xr3:uid="{389D190B-EB55-4CAA-AC9D-5B8FA9A519AA}" name="Inicio_LB_R0" dataDxfId="111"/>
+    <tableColumn id="16" xr3:uid="{106C4044-D370-4038-910C-AB55A197C297}" name="Término_LB_R0" dataDxfId="110"/>
+    <tableColumn id="17" xr3:uid="{6E032648-7E26-4640-B25E-1D062FB90AC7}" name="Sprint" dataDxfId="109"/>
+    <tableColumn id="18" xr3:uid="{690C88D3-1752-4678-8FD4-5DD23108B482}" name="Sucessoras" dataDxfId="108"/>
+    <tableColumn id="19" xr3:uid="{969B9EAF-5B20-495C-88E9-5BE22ACC4024}" name="Comparação" dataDxfId="107"/>
+    <tableColumn id="20" xr3:uid="{D23B245E-A538-4C56-BC73-A2346908CA33}" name="Nomes dos recursos" dataDxfId="106"/>
+    <tableColumn id="21" xr3:uid="{69B56DDE-EDB5-44E3-94A0-9DF32D950B32}" name="pct_val" dataDxfId="105"/>
+    <tableColumn id="22" xr3:uid="{4EB66340-A596-4078-9017-F7D7652830E2}" name="Emissão inicial total" dataDxfId="104"/>
+    <tableColumn id="23" xr3:uid="{41BF6A69-0203-4C01-A6CA-CA19979B2D9D}" name="Emissão inicial concluída" dataDxfId="103"/>
+    <tableColumn id="24" xr3:uid="{8D89AA0A-45FB-47E7-869B-267B596308B1}" name="Emissão Inicial Atrasada" dataDxfId="102"/>
+    <tableColumn id="25" xr3:uid="{9267BD68-23A8-488D-8561-D745A3CB58A6}" name="Aprovação total" dataDxfId="101"/>
+    <tableColumn id="26" xr3:uid="{F6257027-3A28-4907-A379-AB63305CE26F}" name="Avaliação do cliente concluída" dataDxfId="100"/>
+    <tableColumn id="27" xr3:uid="{49084566-DCA6-4F4D-9941-4B6987B7E387}" name="Avaliação Cliente Atrasada" dataDxfId="99"/>
+    <tableColumn id="28" xr3:uid="{BB0306E9-45DB-4AFB-8ECB-C6841821B00F}" name="Atendimento de comentário concluído" dataDxfId="98"/>
+    <tableColumn id="29" xr3:uid="{9F17512D-AEC3-4AA8-BBD2-F52F88C92032}" name="Atendimento Atrasado" dataDxfId="97"/>
+    <tableColumn id="30" xr3:uid="{A28EC239-F3FF-4653-B0ED-7D2A7C9A4047}" name="Aprovação concluída" dataDxfId="96"/>
+    <tableColumn id="31" xr3:uid="{B9B113F3-6B5F-4B16-888C-C5909411106C}" name="Aprovação Atrasada" dataDxfId="95"/>
+    <tableColumn id="32" xr3:uid="{294E4172-9AEE-4190-A6BE-6A07E2931923}" name="Aderência" dataDxfId="94"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4A55F706-9ADB-4D48-A0E3-FA2DAF5514CF}" name="Tabela2" displayName="Tabela2" ref="A3:H17" totalsRowCount="1" headerRowDxfId="118" dataDxfId="117">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4A55F706-9ADB-4D48-A0E3-FA2DAF5514CF}" name="Tabela2" displayName="Tabela2" ref="A3:H17" totalsRowCount="1" headerRowDxfId="93" dataDxfId="92">
   <autoFilter ref="A3:H16" xr:uid="{4A55F706-9ADB-4D48-A0E3-FA2DAF5514CF}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{683BB28D-FBF0-4E0D-A209-3A107077FFAC}" name="Disciplina" totalsRowLabel="TOTAL" dataDxfId="126" totalsRowDxfId="109"/>
-    <tableColumn id="2" xr3:uid="{49D6484B-DF94-44C4-B7FC-9D1B98F1A308}" name="Emissão inicial total" totalsRowFunction="sum" dataDxfId="125" totalsRowDxfId="108"/>
-    <tableColumn id="3" xr3:uid="{BAD0CCC6-A0A8-48CB-8119-F5DD01F29EAF}" name="Emissão inicial concluída" totalsRowFunction="sum" dataDxfId="124" totalsRowDxfId="107"/>
-    <tableColumn id="4" xr3:uid="{A1A02CB2-C181-4F10-8F5B-4507091B05C7}" name="%EI" dataDxfId="123" totalsRowDxfId="103"/>
-    <tableColumn id="5" xr3:uid="{FF69DA53-1E94-498B-A366-B5C8EE4E002F}" name="Avaliação do cliente concluída" totalsRowFunction="sum" dataDxfId="122" totalsRowDxfId="106"/>
-    <tableColumn id="6" xr3:uid="{B9B537AF-9AB0-4265-9DC4-7325E4CA604C}" name="Atendimento de comentário concluído" totalsRowFunction="sum" dataDxfId="121" totalsRowDxfId="105"/>
-    <tableColumn id="7" xr3:uid="{881DD397-E46E-491D-B903-8BB469D9B3E0}" name="Aprovação concluída" totalsRowFunction="sum" dataDxfId="120" totalsRowDxfId="104"/>
-    <tableColumn id="8" xr3:uid="{F87ECD7F-AD84-414D-8424-C952016AAD23}" name="%AP" dataDxfId="119" totalsRowDxfId="102"/>
+    <tableColumn id="1" xr3:uid="{683BB28D-FBF0-4E0D-A209-3A107077FFAC}" name="Disciplina" totalsRowLabel="TOTAL" dataDxfId="91" totalsRowDxfId="90"/>
+    <tableColumn id="2" xr3:uid="{49D6484B-DF94-44C4-B7FC-9D1B98F1A308}" name="Emissão inicial total" totalsRowFunction="sum" dataDxfId="89" totalsRowDxfId="88"/>
+    <tableColumn id="3" xr3:uid="{BAD0CCC6-A0A8-48CB-8119-F5DD01F29EAF}" name="Emissão inicial concluída" totalsRowFunction="sum" dataDxfId="87" totalsRowDxfId="86"/>
+    <tableColumn id="4" xr3:uid="{A1A02CB2-C181-4F10-8F5B-4507091B05C7}" name="%EI" dataDxfId="85" totalsRowDxfId="84"/>
+    <tableColumn id="5" xr3:uid="{FF69DA53-1E94-498B-A366-B5C8EE4E002F}" name="Avaliação do cliente concluída" totalsRowFunction="sum" dataDxfId="83" totalsRowDxfId="82"/>
+    <tableColumn id="6" xr3:uid="{B9B537AF-9AB0-4265-9DC4-7325E4CA604C}" name="Atendimento de comentário concluído" totalsRowFunction="sum" dataDxfId="81" totalsRowDxfId="80"/>
+    <tableColumn id="7" xr3:uid="{881DD397-E46E-491D-B903-8BB469D9B3E0}" name="Aprovação concluída" totalsRowFunction="sum" dataDxfId="79" totalsRowDxfId="78"/>
+    <tableColumn id="8" xr3:uid="{F87ECD7F-AD84-414D-8424-C952016AAD23}" name="%AP" dataDxfId="77" totalsRowDxfId="76"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A5E1BB64-CAE5-4712-A652-BDADC74A670A}" name="Tabela3" displayName="Tabela3" ref="A22:E36" totalsRowCount="1" headerRowDxfId="111" dataDxfId="110">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A5E1BB64-CAE5-4712-A652-BDADC74A670A}" name="Tabela3" displayName="Tabela3" ref="A22:E36" totalsRowCount="1" headerRowDxfId="75" dataDxfId="74">
   <autoFilter ref="A22:E35" xr:uid="{A5E1BB64-CAE5-4712-A652-BDADC74A670A}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{BA10E592-04FD-44D2-8FDB-CA302BB5BBDB}" name="Disciplina" totalsRowLabel="TOTAL" dataDxfId="116" totalsRowDxfId="101"/>
-    <tableColumn id="2" xr3:uid="{5EF10642-BF9E-4CD8-AB0B-A6DC08C5DD66}" name="Emissão Inicial Atrasada" totalsRowFunction="sum" dataDxfId="115" totalsRowDxfId="100"/>
-    <tableColumn id="3" xr3:uid="{7630C206-306D-43A7-BA44-E0BF2C561995}" name="Avaliação Cliente Atrasada" totalsRowFunction="sum" dataDxfId="114" totalsRowDxfId="99"/>
-    <tableColumn id="4" xr3:uid="{89CC1FC9-8C9F-451E-B12F-3BBA6F9FB7BC}" name="Atendimento Atrasado" totalsRowFunction="sum" dataDxfId="113" totalsRowDxfId="98"/>
-    <tableColumn id="5" xr3:uid="{73D79212-6432-4420-9F7C-5974DCA59990}" name="Aprovação Atrasada" totalsRowFunction="sum" dataDxfId="112" totalsRowDxfId="97"/>
+    <tableColumn id="1" xr3:uid="{BA10E592-04FD-44D2-8FDB-CA302BB5BBDB}" name="Disciplina" totalsRowLabel="TOTAL" dataDxfId="73" totalsRowDxfId="72"/>
+    <tableColumn id="2" xr3:uid="{5EF10642-BF9E-4CD8-AB0B-A6DC08C5DD66}" name="Emissão Inicial Atrasada" totalsRowFunction="sum" dataDxfId="71" totalsRowDxfId="70"/>
+    <tableColumn id="3" xr3:uid="{7630C206-306D-43A7-BA44-E0BF2C561995}" name="Avaliação Cliente Atrasada" totalsRowFunction="sum" dataDxfId="69" totalsRowDxfId="68"/>
+    <tableColumn id="4" xr3:uid="{89CC1FC9-8C9F-451E-B12F-3BBA6F9FB7BC}" name="Atendimento Atrasado" totalsRowFunction="sum" dataDxfId="67" totalsRowDxfId="66"/>
+    <tableColumn id="5" xr3:uid="{73D79212-6432-4420-9F7C-5974DCA59990}" name="Aprovação Atrasada" totalsRowFunction="sum" dataDxfId="65" totalsRowDxfId="64"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FA4B19B1-B012-4136-8A8B-BF955F86BF1B}" name="Tabela4" displayName="Tabela4" ref="A1:O183" totalsRowShown="0" headerRowDxfId="90" dataDxfId="89">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{FA4B19B1-B012-4136-8A8B-BF955F86BF1B}" name="Tabela4" displayName="Tabela4" ref="A1:O183" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
   <autoFilter ref="A1:O183" xr:uid="{FA4B19B1-B012-4136-8A8B-BF955F86BF1B}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{A60D7DF6-8205-47D4-9957-B76C4177E6E8}" name="Data" dataDxfId="87"/>
-    <tableColumn id="2" xr3:uid="{9EEC0898-2297-42D8-B624-6DC3AE167662}" name="Emissão prevista na LB" dataDxfId="88"/>
-    <tableColumn id="3" xr3:uid="{2846F61A-9F27-45EE-BF45-58A2001BA8EB}" name="Emissão prevista na LB acumulada" dataDxfId="96"/>
-    <tableColumn id="4" xr3:uid="{82E2C67B-D796-4504-B731-8ED78E7ACD64}" name="Emissão realizada por dia" dataDxfId="95"/>
-    <tableColumn id="5" xr3:uid="{B962B2FB-35EA-461B-831A-24FC6D26670E}" name="Emissão realizada acumulada" dataDxfId="94"/>
-    <tableColumn id="6" xr3:uid="{60752F81-AB0E-48E9-893D-BDF479E42ADB}" name="Aprovação prevista na LB" dataDxfId="93"/>
-    <tableColumn id="7" xr3:uid="{5C2B038B-D974-4A93-81E1-223BE32A4B07}" name="Aprovação realizada por dia" dataDxfId="92"/>
-    <tableColumn id="8" xr3:uid="{7F2A914B-7D2A-4AD7-840D-02C11C71E992}" name="Aprovação prevista na LB acumulada" dataDxfId="91"/>
-    <tableColumn id="9" xr3:uid="{EDC42358-32B3-4F14-AA83-469843A4453E}" name="Aprovação realizada acumulada" dataDxfId="86"/>
-    <tableColumn id="10" xr3:uid="{D332CE9B-E02F-48F0-A6F9-F3AAC672F0F4}" name="Avanço da EI previsto na LB" dataDxfId="85" dataCellStyle="Porcentagem"/>
-    <tableColumn id="11" xr3:uid="{6A6D5B5A-23FF-480D-B7FB-A4CCD3587C72}" name="Avanço real da EI na LB" dataDxfId="84" dataCellStyle="Porcentagem"/>
-    <tableColumn id="12" xr3:uid="{8A0A8487-E2C3-4577-80AA-EB51CE960385}" name="COMP_EI" dataDxfId="83"/>
-    <tableColumn id="13" xr3:uid="{B0230E13-202D-4ACF-8C37-06B526D1EFE3}" name="Avanço da AP previsto na LB" dataDxfId="82" dataCellStyle="Porcentagem"/>
-    <tableColumn id="14" xr3:uid="{57312E3C-4BB5-4F90-92A3-00D85B5D33BC}" name="Avanço da AP real na LB" dataDxfId="80" dataCellStyle="Porcentagem"/>
-    <tableColumn id="15" xr3:uid="{FB381D91-7001-43A2-9AC6-3728825DEF52}" name="COMP_AP" dataDxfId="81"/>
+    <tableColumn id="1" xr3:uid="{A60D7DF6-8205-47D4-9957-B76C4177E6E8}" name="Data" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{9EEC0898-2297-42D8-B624-6DC3AE167662}" name="Emissão prevista na LB" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{2846F61A-9F27-45EE-BF45-58A2001BA8EB}" name="Emissão prevista na LB acumulada" dataDxfId="59"/>
+    <tableColumn id="4" xr3:uid="{82E2C67B-D796-4504-B731-8ED78E7ACD64}" name="Emissão realizada por dia" dataDxfId="58"/>
+    <tableColumn id="5" xr3:uid="{B962B2FB-35EA-461B-831A-24FC6D26670E}" name="Emissão realizada acumulada" dataDxfId="57"/>
+    <tableColumn id="6" xr3:uid="{60752F81-AB0E-48E9-893D-BDF479E42ADB}" name="Aprovação prevista na LB" dataDxfId="56"/>
+    <tableColumn id="7" xr3:uid="{5C2B038B-D974-4A93-81E1-223BE32A4B07}" name="Aprovação realizada por dia" dataDxfId="55"/>
+    <tableColumn id="8" xr3:uid="{7F2A914B-7D2A-4AD7-840D-02C11C71E992}" name="Aprovação prevista na LB acumulada" dataDxfId="54"/>
+    <tableColumn id="9" xr3:uid="{EDC42358-32B3-4F14-AA83-469843A4453E}" name="Aprovação realizada acumulada" dataDxfId="53"/>
+    <tableColumn id="10" xr3:uid="{D332CE9B-E02F-48F0-A6F9-F3AAC672F0F4}" name="Avanço da EI previsto na LB" dataDxfId="52" dataCellStyle="Porcentagem"/>
+    <tableColumn id="11" xr3:uid="{6A6D5B5A-23FF-480D-B7FB-A4CCD3587C72}" name="Avanço real da EI na LB" dataDxfId="51" dataCellStyle="Porcentagem"/>
+    <tableColumn id="12" xr3:uid="{8A0A8487-E2C3-4577-80AA-EB51CE960385}" name="COMP_EI" dataDxfId="50"/>
+    <tableColumn id="13" xr3:uid="{B0230E13-202D-4ACF-8C37-06B526D1EFE3}" name="Avanço da AP previsto na LB" dataDxfId="49" dataCellStyle="Porcentagem"/>
+    <tableColumn id="14" xr3:uid="{57312E3C-4BB5-4F90-92A3-00D85B5D33BC}" name="Avanço da AP real na LB" dataDxfId="48" dataCellStyle="Porcentagem"/>
+    <tableColumn id="15" xr3:uid="{FB381D91-7001-43A2-9AC6-3728825DEF52}" name="COMP_AP" dataDxfId="47"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{C5B0722E-8275-402C-8409-79138840222C}" name="Tabela5" displayName="Tabela5" ref="A1:AF32" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{C5B0722E-8275-402C-8409-79138840222C}" name="Tabela5" displayName="Tabela5" ref="A1:AF32" totalsRowShown="0" headerRowDxfId="161" dataDxfId="160">
   <autoFilter ref="A1:AF32" xr:uid="{C5B0722E-8275-402C-8409-79138840222C}">
     <filterColumn colId="3">
       <filters>
@@ -23164,45 +19166,45 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="32">
-    <tableColumn id="1" xr3:uid="{7C52BE4F-0030-4DF8-B586-DB68D9E2328E}" name="Id" dataDxfId="79"/>
-    <tableColumn id="2" xr3:uid="{B06212AB-78B6-4BF1-96AB-A181B0B58430}" name="EDT" dataDxfId="78"/>
-    <tableColumn id="3" xr3:uid="{8A1C653E-D9CA-48D8-8E0B-087296EF32A7}" name="Nome do Resumo da Tarefa" dataDxfId="77"/>
-    <tableColumn id="4" xr3:uid="{5401C196-A362-47AE-955B-7F995A311DF4}" name="Nome da Tarefa" dataDxfId="76"/>
-    <tableColumn id="5" xr3:uid="{EE7E0DE5-E64B-48C9-BB81-5F23D1054D1C}" name="Título" dataDxfId="75"/>
-    <tableColumn id="6" xr3:uid="{F0784C8C-8EFB-4D61-BECE-2B170308468D}" name="Duração" dataDxfId="52"/>
-    <tableColumn id="7" xr3:uid="{D4BFA9E3-BEAC-414B-AAB7-8A67EA2B0899}" name="Início" dataDxfId="51"/>
-    <tableColumn id="8" xr3:uid="{CD3DA083-71C5-4B95-8971-30E798A29A73}" name="Término" dataDxfId="49"/>
-    <tableColumn id="9" xr3:uid="{1605064B-B30F-4114-9BCA-894E91D39AF8}" name="Predecessoras" dataDxfId="50"/>
-    <tableColumn id="10" xr3:uid="{633F3DF9-D47B-47AB-BBCE-D98F06404058}" name="% concluída" dataDxfId="48" dataCellStyle="Porcentagem"/>
-    <tableColumn id="11" xr3:uid="{5FED373A-16EA-49C5-9BD2-37B75D3590ED}" name="Término real" dataDxfId="46"/>
-    <tableColumn id="12" xr3:uid="{EDF7EDE7-1D71-4BB0-9C0B-E2ECD76121A2}" name="Status" dataDxfId="47"/>
-    <tableColumn id="13" xr3:uid="{B57C7926-8C81-4626-A5ED-CDDAE9FE1B52}" name="Crítica" dataDxfId="74"/>
-    <tableColumn id="14" xr3:uid="{3EF54224-8E0D-4E03-AD90-0BA9039AEB8D}" name="Disciplina" dataDxfId="73"/>
-    <tableColumn id="15" xr3:uid="{FA104353-6A84-4940-984C-786ABF21CFDB}" name="Inicio_LB_R0" dataDxfId="72"/>
-    <tableColumn id="16" xr3:uid="{C86BA5BA-1D0B-4DA8-83B7-80679D97D2B6}" name="Término_LB_R0" dataDxfId="71"/>
-    <tableColumn id="17" xr3:uid="{2221E764-5D7A-4660-A365-628B0D1FEBC9}" name="Sprint" dataDxfId="70"/>
-    <tableColumn id="18" xr3:uid="{F80CCE34-1E8C-4731-B5A2-FCDCE7E8B890}" name="Sucessoras" dataDxfId="69"/>
-    <tableColumn id="19" xr3:uid="{EFF6513A-87BD-41F4-8216-F0051B9FCA4A}" name="Comparação" dataDxfId="68"/>
-    <tableColumn id="20" xr3:uid="{5ED6A974-2240-415C-BB0A-FFF81DAA1390}" name="Nomes dos recursos" dataDxfId="67"/>
-    <tableColumn id="21" xr3:uid="{5234537A-BBED-477B-8FA9-9F7AE34DC2BA}" name="pct_val" dataDxfId="66"/>
-    <tableColumn id="22" xr3:uid="{C318CC64-93AF-41F2-9EBD-DCE5399F8523}" name="Emissão inicial total" dataDxfId="65"/>
-    <tableColumn id="23" xr3:uid="{EAB5387C-824D-4E50-8BC5-4A3F25600014}" name="Emissão inicial concluída" dataDxfId="64"/>
-    <tableColumn id="24" xr3:uid="{F9A439A6-990B-4154-91F2-E3686ECD2F16}" name="Emissão Inicial Atrasada" dataDxfId="63"/>
-    <tableColumn id="25" xr3:uid="{DA1489C5-BC72-428A-B672-EC5B04C5479B}" name="Aprovação total" dataDxfId="62"/>
-    <tableColumn id="26" xr3:uid="{A69503B4-A3D8-4F79-9262-1D8FE0227C5F}" name="Avaliação do cliente concluída" dataDxfId="61"/>
-    <tableColumn id="27" xr3:uid="{29C36A79-B4D3-4C5D-833A-2B352A883FF4}" name="Avaliação Cliente Atrasada" dataDxfId="60"/>
-    <tableColumn id="28" xr3:uid="{AEF84BB6-AC30-4A92-9E8C-6853EC9BDADB}" name="Atendimento de comentário concluído" dataDxfId="59"/>
-    <tableColumn id="29" xr3:uid="{FFF62C55-EA07-4536-A9E4-299ACEFC6551}" name="Atendimento Atrasado" dataDxfId="58"/>
-    <tableColumn id="30" xr3:uid="{0FD2E6F9-277A-4A79-80ED-8D10518EF849}" name="Aprovação concluída" dataDxfId="57"/>
-    <tableColumn id="31" xr3:uid="{F51E0C16-2F5B-47E4-A819-14700E39A14D}" name="Aprovação Atrasada" dataDxfId="56"/>
-    <tableColumn id="32" xr3:uid="{CB759516-B607-43CD-B416-361A11580F54}" name="Aderência" dataDxfId="55"/>
+    <tableColumn id="1" xr3:uid="{7C52BE4F-0030-4DF8-B586-DB68D9E2328E}" name="Id" dataDxfId="159"/>
+    <tableColumn id="2" xr3:uid="{B06212AB-78B6-4BF1-96AB-A181B0B58430}" name="EDT" dataDxfId="158"/>
+    <tableColumn id="3" xr3:uid="{8A1C653E-D9CA-48D8-8E0B-087296EF32A7}" name="Nome do Resumo da Tarefa" dataDxfId="157"/>
+    <tableColumn id="4" xr3:uid="{5401C196-A362-47AE-955B-7F995A311DF4}" name="Nome da Tarefa" dataDxfId="156"/>
+    <tableColumn id="5" xr3:uid="{EE7E0DE5-E64B-48C9-BB81-5F23D1054D1C}" name="Título" dataDxfId="155"/>
+    <tableColumn id="6" xr3:uid="{F0784C8C-8EFB-4D61-BECE-2B170308468D}" name="Duração" dataDxfId="154"/>
+    <tableColumn id="7" xr3:uid="{D4BFA9E3-BEAC-414B-AAB7-8A67EA2B0899}" name="Início" dataDxfId="153"/>
+    <tableColumn id="8" xr3:uid="{CD3DA083-71C5-4B95-8971-30E798A29A73}" name="Término" dataDxfId="152"/>
+    <tableColumn id="9" xr3:uid="{1605064B-B30F-4114-9BCA-894E91D39AF8}" name="Predecessoras" dataDxfId="151"/>
+    <tableColumn id="10" xr3:uid="{633F3DF9-D47B-47AB-BBCE-D98F06404058}" name="% concluída" dataDxfId="150" dataCellStyle="Porcentagem"/>
+    <tableColumn id="11" xr3:uid="{5FED373A-16EA-49C5-9BD2-37B75D3590ED}" name="Término real" dataDxfId="149"/>
+    <tableColumn id="12" xr3:uid="{EDF7EDE7-1D71-4BB0-9C0B-E2ECD76121A2}" name="Status" dataDxfId="148"/>
+    <tableColumn id="13" xr3:uid="{B57C7926-8C81-4626-A5ED-CDDAE9FE1B52}" name="Crítica" dataDxfId="147"/>
+    <tableColumn id="14" xr3:uid="{3EF54224-8E0D-4E03-AD90-0BA9039AEB8D}" name="Disciplina" dataDxfId="146"/>
+    <tableColumn id="15" xr3:uid="{FA104353-6A84-4940-984C-786ABF21CFDB}" name="Inicio_LB_R0" dataDxfId="145"/>
+    <tableColumn id="16" xr3:uid="{C86BA5BA-1D0B-4DA8-83B7-80679D97D2B6}" name="Término_LB_R0" dataDxfId="144"/>
+    <tableColumn id="17" xr3:uid="{2221E764-5D7A-4660-A365-628B0D1FEBC9}" name="Sprint" dataDxfId="143"/>
+    <tableColumn id="18" xr3:uid="{F80CCE34-1E8C-4731-B5A2-FCDCE7E8B890}" name="Sucessoras" dataDxfId="142"/>
+    <tableColumn id="19" xr3:uid="{EFF6513A-87BD-41F4-8216-F0051B9FCA4A}" name="Comparação" dataDxfId="141"/>
+    <tableColumn id="20" xr3:uid="{5ED6A974-2240-415C-BB0A-FFF81DAA1390}" name="Nomes dos recursos" dataDxfId="140"/>
+    <tableColumn id="21" xr3:uid="{5234537A-BBED-477B-8FA9-9F7AE34DC2BA}" name="pct_val" dataDxfId="139"/>
+    <tableColumn id="22" xr3:uid="{C318CC64-93AF-41F2-9EBD-DCE5399F8523}" name="Emissão inicial total" dataDxfId="138"/>
+    <tableColumn id="23" xr3:uid="{EAB5387C-824D-4E50-8BC5-4A3F25600014}" name="Emissão inicial concluída" dataDxfId="137"/>
+    <tableColumn id="24" xr3:uid="{F9A439A6-990B-4154-91F2-E3686ECD2F16}" name="Emissão Inicial Atrasada" dataDxfId="136"/>
+    <tableColumn id="25" xr3:uid="{DA1489C5-BC72-428A-B672-EC5B04C5479B}" name="Aprovação total" dataDxfId="135"/>
+    <tableColumn id="26" xr3:uid="{A69503B4-A3D8-4F79-9262-1D8FE0227C5F}" name="Avaliação do cliente concluída" dataDxfId="134"/>
+    <tableColumn id="27" xr3:uid="{29C36A79-B4D3-4C5D-833A-2B352A883FF4}" name="Avaliação Cliente Atrasada" dataDxfId="133"/>
+    <tableColumn id="28" xr3:uid="{AEF84BB6-AC30-4A92-9E8C-6853EC9BDADB}" name="Atendimento de comentário concluído" dataDxfId="132"/>
+    <tableColumn id="29" xr3:uid="{FFF62C55-EA07-4536-A9E4-299ACEFC6551}" name="Atendimento Atrasado" dataDxfId="131"/>
+    <tableColumn id="30" xr3:uid="{0FD2E6F9-277A-4A79-80ED-8D10518EF849}" name="Aprovação concluída" dataDxfId="130"/>
+    <tableColumn id="31" xr3:uid="{F51E0C16-2F5B-47E4-A819-14700E39A14D}" name="Aprovação Atrasada" dataDxfId="129"/>
+    <tableColumn id="32" xr3:uid="{CB759516-B607-43CD-B416-361A11580F54}" name="Aderência" dataDxfId="128"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{4FBB73B0-888F-4522-B386-138A6A9E9B4F}" name="Tabela6" displayName="Tabela6" ref="A1:AF81" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{4FBB73B0-888F-4522-B386-138A6A9E9B4F}" name="Tabela6" displayName="Tabela6" ref="A1:AF81" totalsRowShown="0" headerRowDxfId="46" dataDxfId="45">
   <autoFilter ref="A1:AF81" xr:uid="{4FBB73B0-888F-4522-B386-138A6A9E9B4F}">
     <filterColumn colId="3">
       <filters>
@@ -23211,63 +19213,64 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="32">
-    <tableColumn id="1" xr3:uid="{A89FA096-DC74-4559-9AE8-C39CD87F05C0}" name="Id" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{73E2CBF2-AD63-436B-B1C1-7CC436496F75}" name="EDT" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{D9A8BBAA-51DB-42E3-84EE-90F4DF773F2C}" name="Nome do Resumo da Tarefa" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{A6280700-2C79-46A5-895A-AA01226437A1}" name="Nome da Tarefa" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{DF19B99F-146E-4978-9B0A-CFE7FBE2F9B4}" name="Título" dataDxfId="41"/>
-    <tableColumn id="6" xr3:uid="{BEA9A507-E9D6-4562-B805-2E8B2E0929F5}" name="Duração" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{FDEB8846-45E3-449F-9064-7DC2647784DE}" name="Início" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{695E461C-FF45-4082-977F-14961FB6BEE7}" name="Término" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{5DD525B8-3C4B-4362-B121-EE4F1449F31E}" name="Predecessoras" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{A37C85B9-14DB-4DA2-9EA1-BD1991F48554}" name="% concluída" dataDxfId="40" dataCellStyle="Porcentagem"/>
-    <tableColumn id="11" xr3:uid="{F0DA60EE-3C40-4291-BB95-4922E4F073F1}" name="Término real" dataDxfId="39"/>
-    <tableColumn id="12" xr3:uid="{83835506-9228-4470-A471-F39942DEEBB1}" name="Status" dataDxfId="38"/>
-    <tableColumn id="13" xr3:uid="{7FC207DE-4A91-4A0A-9223-75B88938FAA5}" name="Crítica" dataDxfId="37"/>
-    <tableColumn id="14" xr3:uid="{1C5E6E81-C67A-4ED7-92EC-0D9C1AE6D439}" name="Disciplina" dataDxfId="36"/>
-    <tableColumn id="15" xr3:uid="{CAD3BF8B-E804-4C83-8153-367259836A74}" name="Inicio_LB_R0" dataDxfId="35"/>
-    <tableColumn id="16" xr3:uid="{EED83361-6659-4E55-B436-D14DDB9A7FD3}" name="Término_LB_R0" dataDxfId="34"/>
-    <tableColumn id="17" xr3:uid="{7287BC8E-E16B-4B33-A0D0-FC9D27CCAFFF}" name="Sprint" dataDxfId="33"/>
-    <tableColumn id="18" xr3:uid="{D8A8421C-1016-4CA5-BABA-57A281CB588A}" name="Sucessoras" dataDxfId="32"/>
-    <tableColumn id="19" xr3:uid="{FF3D380B-352E-4720-9119-169C12AD76B9}" name="Comparação" dataDxfId="31"/>
-    <tableColumn id="20" xr3:uid="{40F51470-6166-43B0-8D65-8FE6C6AB059C}" name="Nomes dos recursos" dataDxfId="30"/>
-    <tableColumn id="21" xr3:uid="{476A2F91-8473-4DE0-AFD8-B07581FD979B}" name="pct_val" dataDxfId="29"/>
-    <tableColumn id="22" xr3:uid="{A4F98346-EBF1-4C9E-8B97-4E3710145B37}" name="Emissão inicial total" dataDxfId="28"/>
-    <tableColumn id="23" xr3:uid="{1900350E-9C1E-4525-AE3A-7D6377379B8D}" name="Emissão inicial concluída" dataDxfId="27"/>
-    <tableColumn id="24" xr3:uid="{885DAF48-7666-4C73-B2D9-4E11B490EF25}" name="Emissão Inicial Atrasada" dataDxfId="26"/>
-    <tableColumn id="25" xr3:uid="{FD2E9DA3-1603-4CD3-81D4-535A3FDCE70F}" name="Aprovação total" dataDxfId="25"/>
-    <tableColumn id="26" xr3:uid="{EC421C62-B8E8-4B98-9D9C-3394210CD082}" name="Avaliação do cliente concluída" dataDxfId="24"/>
-    <tableColumn id="27" xr3:uid="{0C0B9944-DF06-4ED8-B350-85B2D0C16668}" name="Avaliação Cliente Atrasada" dataDxfId="23"/>
-    <tableColumn id="28" xr3:uid="{23445782-7352-4D5D-9652-3E128DF7E553}" name="Atendimento de comentário concluído" dataDxfId="22"/>
-    <tableColumn id="29" xr3:uid="{C0B8A114-82A2-44C3-9F5D-50521889A002}" name="Atendimento Atrasado" dataDxfId="21"/>
-    <tableColumn id="30" xr3:uid="{8282A626-88CF-4DC0-B9FD-8F85C5039CAB}" name="Aprovação concluída" dataDxfId="20"/>
-    <tableColumn id="31" xr3:uid="{3006BB56-DCFD-4FED-AAF6-BA256F1701B3}" name="Aprovação Atrasada" dataDxfId="19"/>
-    <tableColumn id="32" xr3:uid="{20C6AD0C-A004-4379-B3C8-15962E6481B1}" name="Aderência" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{A89FA096-DC74-4559-9AE8-C39CD87F05C0}" name="Id" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{73E2CBF2-AD63-436B-B1C1-7CC436496F75}" name="EDT" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{D9A8BBAA-51DB-42E3-84EE-90F4DF773F2C}" name="Nome do Resumo da Tarefa" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{A6280700-2C79-46A5-895A-AA01226437A1}" name="Nome da Tarefa" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{DF19B99F-146E-4978-9B0A-CFE7FBE2F9B4}" name="Título" dataDxfId="40"/>
+    <tableColumn id="6" xr3:uid="{BEA9A507-E9D6-4562-B805-2E8B2E0929F5}" name="Duração" dataDxfId="39"/>
+    <tableColumn id="7" xr3:uid="{FDEB8846-45E3-449F-9064-7DC2647784DE}" name="Início" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{695E461C-FF45-4082-977F-14961FB6BEE7}" name="Término" dataDxfId="37"/>
+    <tableColumn id="9" xr3:uid="{5DD525B8-3C4B-4362-B121-EE4F1449F31E}" name="Predecessoras" dataDxfId="36"/>
+    <tableColumn id="10" xr3:uid="{A37C85B9-14DB-4DA2-9EA1-BD1991F48554}" name="% concluída" dataDxfId="35" dataCellStyle="Porcentagem"/>
+    <tableColumn id="11" xr3:uid="{F0DA60EE-3C40-4291-BB95-4922E4F073F1}" name="Término real" dataDxfId="34"/>
+    <tableColumn id="12" xr3:uid="{83835506-9228-4470-A471-F39942DEEBB1}" name="Status" dataDxfId="33"/>
+    <tableColumn id="13" xr3:uid="{7FC207DE-4A91-4A0A-9223-75B88938FAA5}" name="Crítica" dataDxfId="32"/>
+    <tableColumn id="14" xr3:uid="{1C5E6E81-C67A-4ED7-92EC-0D9C1AE6D439}" name="Disciplina" dataDxfId="31"/>
+    <tableColumn id="15" xr3:uid="{CAD3BF8B-E804-4C83-8153-367259836A74}" name="Inicio_LB_R0" dataDxfId="30"/>
+    <tableColumn id="16" xr3:uid="{EED83361-6659-4E55-B436-D14DDB9A7FD3}" name="Término_LB_R0" dataDxfId="29"/>
+    <tableColumn id="17" xr3:uid="{7287BC8E-E16B-4B33-A0D0-FC9D27CCAFFF}" name="Sprint" dataDxfId="28"/>
+    <tableColumn id="18" xr3:uid="{D8A8421C-1016-4CA5-BABA-57A281CB588A}" name="Sucessoras" dataDxfId="27"/>
+    <tableColumn id="19" xr3:uid="{FF3D380B-352E-4720-9119-169C12AD76B9}" name="Comparação" dataDxfId="26"/>
+    <tableColumn id="20" xr3:uid="{40F51470-6166-43B0-8D65-8FE6C6AB059C}" name="Nomes dos recursos" dataDxfId="25"/>
+    <tableColumn id="21" xr3:uid="{476A2F91-8473-4DE0-AFD8-B07581FD979B}" name="pct_val" dataDxfId="24"/>
+    <tableColumn id="22" xr3:uid="{A4F98346-EBF1-4C9E-8B97-4E3710145B37}" name="Emissão inicial total" dataDxfId="23"/>
+    <tableColumn id="23" xr3:uid="{1900350E-9C1E-4525-AE3A-7D6377379B8D}" name="Emissão inicial concluída" dataDxfId="22"/>
+    <tableColumn id="24" xr3:uid="{885DAF48-7666-4C73-B2D9-4E11B490EF25}" name="Emissão Inicial Atrasada" dataDxfId="21"/>
+    <tableColumn id="25" xr3:uid="{FD2E9DA3-1603-4CD3-81D4-535A3FDCE70F}" name="Aprovação total" dataDxfId="20"/>
+    <tableColumn id="26" xr3:uid="{EC421C62-B8E8-4B98-9D9C-3394210CD082}" name="Avaliação do cliente concluída" dataDxfId="19"/>
+    <tableColumn id="27" xr3:uid="{0C0B9944-DF06-4ED8-B350-85B2D0C16668}" name="Avaliação Cliente Atrasada" dataDxfId="18"/>
+    <tableColumn id="28" xr3:uid="{23445782-7352-4D5D-9652-3E128DF7E553}" name="Atendimento de comentário concluído" dataDxfId="17"/>
+    <tableColumn id="29" xr3:uid="{C0B8A114-82A2-44C3-9F5D-50521889A002}" name="Atendimento Atrasado" dataDxfId="16"/>
+    <tableColumn id="30" xr3:uid="{8282A626-88CF-4DC0-B9FD-8F85C5039CAB}" name="Aprovação concluída" dataDxfId="15"/>
+    <tableColumn id="31" xr3:uid="{3006BB56-DCFD-4FED-AAF6-BA256F1701B3}" name="Aprovação Atrasada" dataDxfId="14"/>
+    <tableColumn id="32" xr3:uid="{20C6AD0C-A004-4379-B3C8-15962E6481B1}" name="Aderência" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1B9E34CA-408D-4A11-8213-2D140CF4CFD5}" name="Tabela7" displayName="Tabela7" ref="A1:J92" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
-  <autoFilter ref="A1:J92" xr:uid="{1B9E34CA-408D-4A11-8213-2D140CF4CFD5}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1B9E34CA-408D-4A11-8213-2D140CF4CFD5}" name="Tabela7" displayName="Tabela7" ref="A1:K92" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="A1:K92" xr:uid="{1B9E34CA-408D-4A11-8213-2D140CF4CFD5}">
     <filterColumn colId="4">
       <filters>
         <filter val="emissão inicial"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{7BFE4D8E-68C9-492F-AAA9-15E7559F9A42}" name="Sprint" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{963F4600-5721-4A62-9F40-3E44A9EE0140}" name="Id" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{5A60FC3D-2FBC-4CED-B50F-F2DED560FBE2}" name="EDT" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{9A7F9B74-67F4-4675-A4D6-729A081033EC}" name="Nome do Resumo da Tarefa" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{C1F76C14-6865-4605-83AD-902D99E5ADBC}" name="Nome da Tarefa" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{A02F2BEA-5753-4FAB-8699-CC378BD4DA85}" name="Status" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{C2F7BF86-0036-4110-88D3-34F5018F7B4A}" name="% concluída" dataDxfId="5" dataCellStyle="Porcentagem"/>
-    <tableColumn id="8" xr3:uid="{2B7D1741-5AE5-4D37-BE90-C0CF5F633EEE}" name="Nomes dos recursos" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{F7B5B94F-CF9C-432C-B46B-BA813612351A}" name="Disciplina" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{27304237-1DCC-423B-8778-D35C3F95FDDD}" name="Crítica" dataDxfId="2"/>
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{7BFE4D8E-68C9-492F-AAA9-15E7559F9A42}" name="Sprint" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{963F4600-5721-4A62-9F40-3E44A9EE0140}" name="Id" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{5A60FC3D-2FBC-4CED-B50F-F2DED560FBE2}" name="EDT" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{9A7F9B74-67F4-4675-A4D6-729A081033EC}" name="Nome do Resumo da Tarefa" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{C1F76C14-6865-4605-83AD-902D99E5ADBC}" name="Nome da Tarefa" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{A02F2BEA-5753-4FAB-8699-CC378BD4DA85}" name="Status" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{C2F7BF86-0036-4110-88D3-34F5018F7B4A}" name="% concluída" dataDxfId="4" dataCellStyle="Porcentagem"/>
+    <tableColumn id="8" xr3:uid="{2B7D1741-5AE5-4D37-BE90-C0CF5F633EEE}" name="Nomes dos recursos" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{F7B5B94F-CF9C-432C-B46B-BA813612351A}" name="Disciplina" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{27304237-1DCC-423B-8778-D35C3F95FDDD}" name="Crítica" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{556E4264-DD42-4A79-9445-59E0746FADB3}" name="Coluna1" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -39661,7 +35664,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="B17" s="1">
         <f>SUBTOTAL(109,Tabela2[Emissão inicial total])</f>
@@ -39926,7 +35929,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="B36" s="1">
         <f>SUBTOTAL(109,Tabela3[Emissão Inicial Atrasada])</f>
@@ -48183,6 +44186,22 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="1" id="{B7D95E84-BD2F-44F4-8D9E-55F661358BA2}">
+            <x14:iconSet iconSet="3Triangles">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>33</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>67</xm:f>
+              </x14:cfvo>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>L1:L187</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="2" id="{1079B480-5000-4614-A3A8-44C8E6EB56D7}">
             <x14:iconSet iconSet="3Triangles">
               <x14:cfvo type="percent">
@@ -48197,22 +44216,6 @@
             </x14:iconSet>
           </x14:cfRule>
           <xm:sqref>O1:O187</xm:sqref>
-        </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="1" id="{B7D95E84-BD2F-44F4-8D9E-55F661358BA2}">
-            <x14:iconSet iconSet="3Triangles">
-              <x14:cfvo type="percent">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="percent">
-                <xm:f>33</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="percent">
-                <xm:f>67</xm:f>
-              </x14:cfvo>
-            </x14:iconSet>
-          </x14:cfRule>
-          <xm:sqref>L1:L187</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -58014,7 +54017,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:K92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -58027,10 +54030,11 @@
     <col min="8" max="8" width="23.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="32.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="1"/>
+    <col min="11" max="11" width="17.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -58061,8 +54065,11 @@
       <c r="J1" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="K1" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>38</v>
       </c>
@@ -58088,7 +54095,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>38</v>
       </c>
@@ -58117,7 +54124,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>38</v>
       </c>
@@ -58146,7 +54153,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>38</v>
       </c>
@@ -58175,7 +54182,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>38</v>
       </c>
@@ -58204,7 +54211,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>38</v>
       </c>
@@ -58233,7 +54240,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>38</v>
       </c>
@@ -58262,7 +54269,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>38</v>
       </c>
@@ -58291,7 +54298,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>38</v>
       </c>
@@ -58320,7 +54327,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>38</v>
       </c>
@@ -58349,7 +54356,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>38</v>
       </c>
@@ -58378,7 +54385,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>38</v>
       </c>
@@ -58407,7 +54414,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>38</v>
       </c>
@@ -58427,7 +54434,7 @@
         <v>34</v>
       </c>
       <c r="G14" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>121</v>
@@ -58435,8 +54442,11 @@
       <c r="J14" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="K14" s="12">
+        <v>46210</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>38</v>
       </c>
@@ -58465,7 +54475,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>38</v>
       </c>
@@ -58494,7 +54504,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>38</v>
       </c>
@@ -58523,7 +54533,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>38</v>
       </c>
@@ -58552,7 +54562,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>29</v>
       </c>
@@ -58577,8 +54587,11 @@
       <c r="J19" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="K19" s="1" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>30</v>
       </c>
@@ -58604,7 +54617,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>31</v>
       </c>
@@ -58630,7 +54643,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>32</v>
       </c>
@@ -58656,7 +54669,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>38</v>
       </c>
@@ -58685,7 +54698,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>38</v>
       </c>
@@ -58714,7 +54727,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>38</v>
       </c>
@@ -58743,7 +54756,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>38</v>
       </c>
@@ -58772,7 +54785,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>38</v>
       </c>
@@ -58801,7 +54814,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>38</v>
       </c>
@@ -58830,7 +54843,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>38</v>
       </c>
@@ -58859,7 +54872,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>38</v>
       </c>
@@ -58888,7 +54901,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>38</v>
       </c>
@@ -58916,8 +54929,11 @@
       <c r="J31" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="K31" s="1" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>38</v>
       </c>
@@ -58946,7 +54962,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>38</v>
       </c>
@@ -58975,7 +54991,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>38</v>
       </c>
@@ -59004,7 +55020,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>38</v>
       </c>
@@ -59033,7 +55049,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>38</v>
       </c>
@@ -59062,7 +55078,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>38</v>
       </c>
@@ -59091,7 +55107,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>38</v>
       </c>
@@ -59120,7 +55136,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>38</v>
       </c>
@@ -59149,7 +55165,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>38</v>
       </c>
@@ -59178,7 +55194,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>38</v>
       </c>
@@ -59207,7 +55223,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>38</v>
       </c>
@@ -59236,7 +55252,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>38</v>
       </c>
@@ -59265,7 +55281,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>38</v>
       </c>
@@ -59294,7 +55310,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>38</v>
       </c>
@@ -59323,7 +55339,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>38</v>
       </c>
@@ -59351,8 +55367,11 @@
       <c r="J46" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="K46" s="1" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>38</v>
       </c>
@@ -59381,7 +55400,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>38</v>
       </c>
@@ -59410,7 +55429,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>38</v>
       </c>
@@ -59439,7 +55458,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>38</v>
       </c>
@@ -59468,7 +55487,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>38</v>
       </c>
@@ -59497,7 +55516,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>38</v>
       </c>
@@ -59525,8 +55544,11 @@
       <c r="J52" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="K52" s="12">
+        <v>46225</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>38</v>
       </c>
@@ -59555,7 +55577,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>38</v>
       </c>
@@ -59584,7 +55606,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>38</v>
       </c>
@@ -59613,7 +55635,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>38</v>
       </c>
@@ -59642,7 +55664,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>38</v>
       </c>
@@ -59671,7 +55693,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>38</v>
       </c>
@@ -59691,7 +55713,7 @@
         <v>64</v>
       </c>
       <c r="G58" s="11">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>321</v>
@@ -59699,8 +55721,11 @@
       <c r="J58" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="K58" s="12">
+        <v>46211</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>38</v>
       </c>
@@ -59729,7 +55754,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>38</v>
       </c>
@@ -59758,7 +55783,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>38</v>
       </c>
@@ -59787,7 +55812,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>38</v>
       </c>
@@ -59816,7 +55841,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>38</v>
       </c>
@@ -59836,7 +55861,7 @@
         <v>34</v>
       </c>
       <c r="G63" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>321</v>
@@ -59844,8 +55869,11 @@
       <c r="J63" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="K63" s="12">
+        <v>46216</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>38</v>
       </c>
@@ -59874,7 +55902,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>38</v>
       </c>
@@ -59903,7 +55931,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>38</v>
       </c>
@@ -59932,7 +55960,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>38</v>
       </c>
@@ -59961,7 +55989,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>38</v>
       </c>
@@ -59990,7 +56018,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>38</v>
       </c>
@@ -60019,7 +56047,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>38</v>
       </c>
@@ -60048,7 +56076,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>38</v>
       </c>
@@ -60077,7 +56105,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>38</v>
       </c>
@@ -60105,8 +56133,11 @@
       <c r="J72" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="K72" s="1" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>38</v>
       </c>
@@ -60135,7 +56166,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>38</v>
       </c>
@@ -60164,7 +56195,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>38</v>
       </c>
@@ -60193,7 +56224,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>38</v>
       </c>
@@ -60222,7 +56253,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>38</v>
       </c>
@@ -60251,7 +56282,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>38</v>
       </c>
@@ -60280,7 +56311,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>38</v>
       </c>
@@ -60309,7 +56340,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>38</v>
       </c>
@@ -60338,7 +56369,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>38</v>
       </c>
@@ -60367,7 +56398,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>38</v>
       </c>
@@ -60396,7 +56427,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>38</v>
       </c>
@@ -60425,7 +56456,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>38</v>
       </c>
@@ -60445,7 +56476,7 @@
         <v>34</v>
       </c>
       <c r="G84" s="11">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>380</v>
@@ -60453,8 +56484,11 @@
       <c r="J84" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="K84" s="12">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>38</v>
       </c>
@@ -60483,7 +56517,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>38</v>
       </c>
@@ -60512,7 +56546,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>38</v>
       </c>
@@ -60541,7 +56575,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>38</v>
       </c>
@@ -60570,7 +56604,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>38</v>
       </c>
@@ -60599,7 +56633,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>38</v>
       </c>
@@ -60628,7 +56662,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>38</v>
       </c>
@@ -60657,7 +56691,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>38</v>
       </c>
@@ -60776,6 +56810,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="c6385d03-c98b-47a8-b084-660309c480c9">
@@ -60784,15 +56827,6 @@
     <TaxCatchAll xmlns="1dad954f-e29e-48a7-b9b8-f0523de1045f" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -60985,20 +57019,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75B7C4F4-61BA-49E6-AF40-8D6526BFFB90}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B8D2EEB-AB90-4499-8353-FFD29DD613E4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="c6385d03-c98b-47a8-b084-660309c480c9"/>
     <ds:schemaRef ds:uri="1dad954f-e29e-48a7-b9b8-f0523de1045f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75B7C4F4-61BA-49E6-AF40-8D6526BFFB90}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
